--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -160,22 +160,28 @@
     <t>Traditional starter</t>
   </si>
   <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>posted</t>
+  </si>
+  <si>
+    <t>Clay Holmes</t>
+  </si>
+  <si>
+    <t>Chase Burns</t>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Cincinnati Reds</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
   </si>
   <si>
     <t>projected_regulars</t>
-  </si>
-  <si>
-    <t>Clay Holmes</t>
-  </si>
-  <si>
-    <t>Chase Burns</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Cincinnati Reds</t>
   </si>
   <si>
     <t>Sandy Alcantara</t>
@@ -815,13 +821,13 @@
         <v>4.5</v>
       </c>
       <c r="D2">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E2">
-        <v>-125</v>
+        <v>-120</v>
       </c>
       <c r="F2">
-        <v>5.19</v>
+        <v>4.97</v>
       </c>
       <c r="H2" t="s">
         <v>45</v>
@@ -830,7 +836,7 @@
         <v>45</v>
       </c>
       <c r="K2">
-        <v>5.19</v>
+        <v>4.97</v>
       </c>
       <c r="L2" t="s">
         <v>46</v>
@@ -881,16 +887,16 @@
         <v>4.4</v>
       </c>
       <c r="AB2">
-        <v>1.0348</v>
+        <v>1.0104</v>
       </c>
       <c r="AC2" t="s">
         <v>49</v>
       </c>
       <c r="AD2">
-        <v>0.2295</v>
+        <v>0.2231</v>
       </c>
       <c r="AE2">
-        <v>0.2286</v>
+        <v>0.2252</v>
       </c>
       <c r="AF2">
         <v>9</v>
@@ -899,10 +905,10 @@
         <v>0.2181</v>
       </c>
       <c r="AH2">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI2">
-        <v>0.9927</v>
+        <v>0.975</v>
       </c>
       <c r="AJ2" t="b">
         <v>1</v>
@@ -931,10 +937,10 @@
         <v>-135</v>
       </c>
       <c r="E3">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>4.63</v>
+        <v>4.04</v>
       </c>
       <c r="H3" t="s">
         <v>45</v>
@@ -943,7 +949,7 @@
         <v>45</v>
       </c>
       <c r="K3">
-        <v>4.63</v>
+        <v>4.04</v>
       </c>
       <c r="L3" t="s">
         <v>46</v>
@@ -994,28 +1000,28 @@
         <v>4.11</v>
       </c>
       <c r="AB3">
-        <v>0.9307</v>
+        <v>0.8409</v>
       </c>
       <c r="AC3" t="s">
         <v>49</v>
       </c>
       <c r="AD3">
-        <v>0.2064</v>
+        <v>0.1857</v>
       </c>
       <c r="AE3">
-        <v>0.1928</v>
+        <v>0.1897</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG3">
         <v>0.2128</v>
       </c>
       <c r="AH3">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI3">
-        <v>1.0046</v>
+        <v>0.9708</v>
       </c>
       <c r="AJ3" t="b">
         <v>1</v>
@@ -1041,13 +1047,13 @@
         <v>6.5</v>
       </c>
       <c r="D4">
-        <v>-104</v>
+        <v>-106</v>
       </c>
       <c r="E4">
         <v>-115</v>
       </c>
       <c r="F4">
-        <v>6.45</v>
+        <v>6.48</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
@@ -1056,7 +1062,7 @@
         <v>45</v>
       </c>
       <c r="K4">
-        <v>6.45</v>
+        <v>6.48</v>
       </c>
       <c r="L4" t="s">
         <v>53</v>
@@ -1107,10 +1113,10 @@
         <v>4.05</v>
       </c>
       <c r="AB4">
-        <v>1.0893</v>
+        <v>1.0941</v>
       </c>
       <c r="AC4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD4">
         <v>0.2416</v>
@@ -1125,7 +1131,7 @@
         <v>0.2108</v>
       </c>
       <c r="AH4">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI4">
         <v>0.9639</v>
@@ -1134,10 +1140,10 @@
         <v>1</v>
       </c>
       <c r="AK4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1148,19 +1154,19 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-109</v>
+        <v>-125</v>
       </c>
       <c r="E5">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F5">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="s">
         <v>45</v>
@@ -1169,7 +1175,7 @@
         <v>45</v>
       </c>
       <c r="K5">
-        <v>6.37</v>
+        <v>6.4</v>
       </c>
       <c r="L5" t="s">
         <v>53</v>
@@ -1220,10 +1226,10 @@
         <v>4.12</v>
       </c>
       <c r="AB5">
-        <v>1.1483</v>
+        <v>1.1533</v>
       </c>
       <c r="AC5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD5">
         <v>0.2547</v>
@@ -1238,7 +1244,7 @@
         <v>0.2548</v>
       </c>
       <c r="AH5">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI5">
         <v>1.033</v>
@@ -1247,10 +1253,10 @@
         <v>1</v>
       </c>
       <c r="AK5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1261,19 +1267,19 @@
         <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C6">
         <v>4.5</v>
       </c>
       <c r="D6">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="E6">
-        <v>-155</v>
+        <v>-146</v>
       </c>
       <c r="F6">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="H6" t="s">
         <v>45</v>
@@ -1282,13 +1288,13 @@
         <v>45</v>
       </c>
       <c r="K6">
-        <v>4.02</v>
+        <v>4.03</v>
       </c>
       <c r="L6" t="s">
         <v>46</v>
       </c>
       <c r="M6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N6">
         <v>823346</v>
@@ -1333,10 +1339,10 @@
         <v>3.98</v>
       </c>
       <c r="AB6">
-        <v>0.9793</v>
+        <v>0.9836</v>
       </c>
       <c r="AC6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD6">
         <v>0.2172</v>
@@ -1351,7 +1357,7 @@
         <v>0.2568</v>
       </c>
       <c r="AH6">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI6">
         <v>1.0072</v>
@@ -1360,10 +1366,10 @@
         <v>1</v>
       </c>
       <c r="AK6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL6" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM6">
         <v>0</v>
@@ -1374,7 +1380,7 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1383,10 +1389,10 @@
         <v>116</v>
       </c>
       <c r="E7">
-        <v>-147</v>
+        <v>-141</v>
       </c>
       <c r="F7">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="H7" t="s">
         <v>45</v>
@@ -1395,13 +1401,13 @@
         <v>45</v>
       </c>
       <c r="K7">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="L7" t="s">
         <v>46</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N7">
         <v>823346</v>
@@ -1446,10 +1452,10 @@
         <v>4.37</v>
       </c>
       <c r="AB7">
-        <v>0.847</v>
+        <v>0.8508</v>
       </c>
       <c r="AC7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD7">
         <v>0.1879</v>
@@ -1464,7 +1470,7 @@
         <v>0.2165</v>
       </c>
       <c r="AH7">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI7">
         <v>0.9858</v>
@@ -1473,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="AK7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM7">
         <v>0</v>
@@ -1487,13 +1493,13 @@
         <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C8">
         <v>4.5</v>
       </c>
       <c r="D8">
-        <v>102</v>
+        <v>-105</v>
       </c>
       <c r="E8">
         <v>-112</v>
@@ -1508,7 +1514,7 @@
         <v>45</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N8" t="s">
         <v>45</v>
@@ -1537,7 +1543,7 @@
         <v>43</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C9">
         <v>7.5</v>
@@ -1549,7 +1555,7 @@
         <v>-155</v>
       </c>
       <c r="F9">
-        <v>5.91</v>
+        <v>5.94</v>
       </c>
       <c r="H9" t="s">
         <v>45</v>
@@ -1558,13 +1564,13 @@
         <v>45</v>
       </c>
       <c r="K9">
-        <v>5.91</v>
+        <v>5.94</v>
       </c>
       <c r="L9" t="s">
         <v>46</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N9">
         <v>824399</v>
@@ -1609,10 +1615,10 @@
         <v>3.96</v>
       </c>
       <c r="AB9">
-        <v>0.6782</v>
+        <v>0.6812</v>
       </c>
       <c r="AC9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD9">
         <v>0.1504</v>
@@ -1627,7 +1633,7 @@
         <v>0.2186</v>
       </c>
       <c r="AH9">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI9">
         <v>0.9884</v>
@@ -1636,10 +1642,10 @@
         <v>1</v>
       </c>
       <c r="AK9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1650,7 +1656,7 @@
         <v>43</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1662,7 +1668,7 @@
         <v>132</v>
       </c>
       <c r="F10">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
       <c r="H10" t="s">
         <v>45</v>
@@ -1671,13 +1677,13 @@
         <v>45</v>
       </c>
       <c r="K10">
-        <v>4.89</v>
+        <v>4.91</v>
       </c>
       <c r="L10" t="s">
         <v>46</v>
       </c>
       <c r="M10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N10">
         <v>824399</v>
@@ -1722,10 +1728,10 @@
         <v>4.1</v>
       </c>
       <c r="AB10">
-        <v>0.9718</v>
+        <v>0.9761</v>
       </c>
       <c r="AC10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD10">
         <v>0.2156</v>
@@ -1740,7 +1746,7 @@
         <v>0.2141</v>
       </c>
       <c r="AH10">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI10">
         <v>0.9615</v>
@@ -1749,10 +1755,10 @@
         <v>1</v>
       </c>
       <c r="AK10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL10" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM10">
         <v>0</v>
@@ -1763,7 +1769,7 @@
         <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1784,7 +1790,7 @@
         <v>45</v>
       </c>
       <c r="M11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N11" t="s">
         <v>45</v>
@@ -1813,7 +1819,7 @@
         <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12">
         <v>4.5</v>
@@ -1825,7 +1831,7 @@
         <v>-125</v>
       </c>
       <c r="F12">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="H12" t="s">
         <v>45</v>
@@ -1834,13 +1840,13 @@
         <v>45</v>
       </c>
       <c r="K12">
-        <v>4.44</v>
+        <v>4.46</v>
       </c>
       <c r="L12" t="s">
         <v>46</v>
       </c>
       <c r="M12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N12">
         <v>823591</v>
@@ -1885,10 +1891,10 @@
         <v>4.27</v>
       </c>
       <c r="AB12">
-        <v>1.135</v>
+        <v>1.1399</v>
       </c>
       <c r="AC12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD12">
         <v>0.2518</v>
@@ -1903,7 +1909,7 @@
         <v>0.2293</v>
       </c>
       <c r="AH12">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI12">
         <v>0.989</v>
@@ -1912,10 +1918,10 @@
         <v>1</v>
       </c>
       <c r="AK12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL12" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM12">
         <v>0</v>
@@ -1926,49 +1932,112 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>6.5</v>
       </c>
       <c r="D13">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="E13">
         <v>-104</v>
       </c>
+      <c r="F13">
+        <v>5.46</v>
+      </c>
       <c r="H13" t="s">
         <v>45</v>
       </c>
       <c r="J13" t="s">
         <v>45</v>
       </c>
+      <c r="K13">
+        <v>5.46</v>
+      </c>
       <c r="L13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
-      </c>
-      <c r="N13" t="s">
-        <v>45</v>
+        <v>70</v>
+      </c>
+      <c r="N13">
+        <v>824882</v>
       </c>
       <c r="O13" t="s">
-        <v>45</v>
+        <v>48</v>
+      </c>
+      <c r="P13">
+        <v>5.9</v>
+      </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13" t="b">
+        <v>0</v>
       </c>
       <c r="S13">
         <v>6</v>
       </c>
+      <c r="T13">
+        <v>0.3057</v>
+      </c>
+      <c r="U13">
+        <v>0.3316</v>
+      </c>
+      <c r="V13">
+        <v>5</v>
+      </c>
+      <c r="W13">
+        <v>102</v>
+      </c>
+      <c r="X13">
+        <v>0.3824</v>
+      </c>
+      <c r="Y13">
+        <v>0.338</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>4.02</v>
+      </c>
+      <c r="AB13">
+        <v>0.7713</v>
+      </c>
       <c r="AC13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="AD13">
+        <v>0.1703</v>
+      </c>
+      <c r="AE13">
+        <v>0.1681</v>
+      </c>
+      <c r="AF13">
+        <v>9</v>
+      </c>
+      <c r="AG13">
+        <v>0.1705</v>
+      </c>
+      <c r="AH13">
+        <v>0.2208</v>
+      </c>
+      <c r="AI13">
+        <v>0.9069</v>
+      </c>
+      <c r="AJ13" t="b">
+        <v>1</v>
       </c>
       <c r="AK13" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="AL13" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
@@ -1976,7 +2045,7 @@
         <v>43</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14">
         <v>3.5</v>
@@ -1985,10 +2054,10 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>-113</v>
+        <v>-105</v>
       </c>
       <c r="F14">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="H14" t="s">
         <v>45</v>
@@ -1997,13 +2066,13 @@
         <v>45</v>
       </c>
       <c r="K14">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="L14" t="s">
         <v>46</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N14">
         <v>824882</v>
@@ -2048,10 +2117,10 @@
         <v>4.16</v>
       </c>
       <c r="AB14">
-        <v>1.0262</v>
+        <v>1.0307</v>
       </c>
       <c r="AC14" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD14">
         <v>0.2276</v>
@@ -2066,7 +2135,7 @@
         <v>0.2174</v>
       </c>
       <c r="AH14">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI14">
         <v>0.9816</v>
@@ -2075,10 +2144,10 @@
         <v>1</v>
       </c>
       <c r="AK14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL14" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM14">
         <v>0</v>
@@ -2089,7 +2158,7 @@
         <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15">
         <v>5.5</v>
@@ -2098,10 +2167,10 @@
         <v>130</v>
       </c>
       <c r="E15">
-        <v>-155</v>
+        <v>-152</v>
       </c>
       <c r="F15">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="H15" t="s">
         <v>45</v>
@@ -2110,13 +2179,13 @@
         <v>45</v>
       </c>
       <c r="K15">
-        <v>5.71</v>
+        <v>5.73</v>
       </c>
       <c r="L15" t="s">
         <v>46</v>
       </c>
       <c r="M15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N15">
         <v>822777</v>
@@ -2161,10 +2230,10 @@
         <v>4.08</v>
       </c>
       <c r="AB15">
-        <v>0.8654</v>
+        <v>0.8692</v>
       </c>
       <c r="AC15" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD15">
         <v>0.1919</v>
@@ -2179,7 +2248,7 @@
         <v>0.1887</v>
       </c>
       <c r="AH15">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI15">
         <v>0.9732</v>
@@ -2188,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="AK15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL15" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM15">
         <v>0</v>
@@ -2202,19 +2271,19 @@
         <v>43</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C16">
         <v>5.5</v>
       </c>
       <c r="D16">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E16">
         <v>-158</v>
       </c>
       <c r="F16">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
@@ -2223,13 +2292,13 @@
         <v>45</v>
       </c>
       <c r="K16">
-        <v>4.53</v>
+        <v>4.55</v>
       </c>
       <c r="L16" t="s">
         <v>46</v>
       </c>
       <c r="M16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N16">
         <v>822777</v>
@@ -2274,10 +2343,10 @@
         <v>4.57</v>
       </c>
       <c r="AB16">
-        <v>1.2427</v>
+        <v>1.2482</v>
       </c>
       <c r="AC16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD16">
         <v>0.2757</v>
@@ -2292,7 +2361,7 @@
         <v>0.2442</v>
       </c>
       <c r="AH16">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI16">
         <v>1.0039</v>
@@ -2301,10 +2370,10 @@
         <v>1</v>
       </c>
       <c r="AK16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL16" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM16">
         <v>0</v>
@@ -2315,19 +2384,19 @@
         <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C17">
         <v>4.5</v>
       </c>
       <c r="D17">
-        <v>-155</v>
+        <v>-150</v>
       </c>
       <c r="E17">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="F17">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="H17" t="s">
         <v>45</v>
@@ -2336,13 +2405,13 @@
         <v>45</v>
       </c>
       <c r="K17">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="L17" t="s">
         <v>46</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N17">
         <v>824159</v>
@@ -2387,10 +2456,10 @@
         <v>4.15</v>
       </c>
       <c r="AB17">
-        <v>0.8956</v>
+        <v>0.8995</v>
       </c>
       <c r="AC17" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD17">
         <v>0.1987</v>
@@ -2405,7 +2474,7 @@
         <v>0.2256</v>
       </c>
       <c r="AH17">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI17">
         <v>0.9876</v>
@@ -2414,10 +2483,10 @@
         <v>1</v>
       </c>
       <c r="AK17" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL17" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM17">
         <v>0</v>
@@ -2428,7 +2497,7 @@
         <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2440,7 +2509,7 @@
         <v>128</v>
       </c>
       <c r="F18">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="H18" t="s">
         <v>45</v>
@@ -2449,13 +2518,13 @@
         <v>45</v>
       </c>
       <c r="K18">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="L18" t="s">
         <v>46</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N18">
         <v>824159</v>
@@ -2500,10 +2569,10 @@
         <v>4.11</v>
       </c>
       <c r="AB18">
-        <v>0.9612</v>
+        <v>0.9655</v>
       </c>
       <c r="AC18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD18">
         <v>0.2132</v>
@@ -2518,7 +2587,7 @@
         <v>0.2162</v>
       </c>
       <c r="AH18">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI18">
         <v>1.0104</v>
@@ -2527,10 +2596,10 @@
         <v>1</v>
       </c>
       <c r="AK18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL18" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM18">
         <v>0</v>
@@ -2541,19 +2610,19 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C19">
         <v>5.5</v>
       </c>
       <c r="D19">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E19">
-        <v>-157</v>
+        <v>-164</v>
       </c>
       <c r="F19">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="H19" t="s">
         <v>45</v>
@@ -2562,13 +2631,13 @@
         <v>45</v>
       </c>
       <c r="K19">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="L19" t="s">
         <v>46</v>
       </c>
       <c r="M19" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N19">
         <v>823993</v>
@@ -2613,10 +2682,10 @@
         <v>4.62</v>
       </c>
       <c r="AB19">
-        <v>0.909</v>
+        <v>0.913</v>
       </c>
       <c r="AC19" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD19">
         <v>0.2016</v>
@@ -2631,7 +2700,7 @@
         <v>0.2092</v>
       </c>
       <c r="AH19">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI19">
         <v>0.9531</v>
@@ -2640,10 +2709,10 @@
         <v>1</v>
       </c>
       <c r="AK19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL19" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM19">
         <v>0</v>
@@ -2654,19 +2723,19 @@
         <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-148</v>
+        <v>-132</v>
       </c>
       <c r="E20">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F20">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="H20" t="s">
         <v>45</v>
@@ -2675,13 +2744,13 @@
         <v>45</v>
       </c>
       <c r="K20">
-        <v>5.06</v>
+        <v>5.08</v>
       </c>
       <c r="L20" t="s">
         <v>46</v>
       </c>
       <c r="M20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N20">
         <v>823993</v>
@@ -2726,10 +2795,10 @@
         <v>4.25</v>
       </c>
       <c r="AB20">
-        <v>1.2184</v>
+        <v>1.2237</v>
       </c>
       <c r="AC20" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD20">
         <v>0.2703</v>
@@ -2744,7 +2813,7 @@
         <v>0.2508</v>
       </c>
       <c r="AH20">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI20">
         <v>1.0327</v>
@@ -2753,10 +2822,10 @@
         <v>1</v>
       </c>
       <c r="AK20" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL20" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM20">
         <v>0</v>
@@ -2767,16 +2836,16 @@
         <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C21">
         <v>5.5</v>
       </c>
       <c r="D21">
-        <v>-140</v>
+        <v>-147</v>
       </c>
       <c r="E21">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H21" t="s">
         <v>45</v>
@@ -2788,7 +2857,7 @@
         <v>45</v>
       </c>
       <c r="M21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N21" t="s">
         <v>45</v>
@@ -2797,7 +2866,7 @@
         <v>45</v>
       </c>
       <c r="S21">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC21" t="s">
         <v>45</v>
@@ -2817,7 +2886,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C22">
         <v>4.5</v>
@@ -2826,10 +2895,10 @@
         <v>120</v>
       </c>
       <c r="E22">
-        <v>-130</v>
+        <v>-128</v>
       </c>
       <c r="F22">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="H22" t="s">
         <v>45</v>
@@ -2838,13 +2907,13 @@
         <v>45</v>
       </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5.73</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
       <c r="M22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N22">
         <v>824968</v>
@@ -2862,7 +2931,7 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T22">
         <v>0.2141</v>
@@ -2889,10 +2958,10 @@
         <v>4.33</v>
       </c>
       <c r="AB22">
-        <v>1.1734</v>
+        <v>1.1785</v>
       </c>
       <c r="AC22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD22">
         <v>0.2603</v>
@@ -2907,7 +2976,7 @@
         <v>0.2168</v>
       </c>
       <c r="AH22">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI22">
         <v>1.013</v>
@@ -2916,10 +2985,10 @@
         <v>1</v>
       </c>
       <c r="AK22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL22" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM22">
         <v>0</v>
@@ -2930,7 +2999,7 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C23">
         <v>6.5</v>
@@ -2939,10 +3008,10 @@
         <v>-125</v>
       </c>
       <c r="E23">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F23">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="H23" t="s">
         <v>45</v>
@@ -2951,13 +3020,13 @@
         <v>45</v>
       </c>
       <c r="K23">
-        <v>5.19</v>
+        <v>5.21</v>
       </c>
       <c r="L23" t="s">
         <v>46</v>
       </c>
       <c r="M23" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N23">
         <v>823913</v>
@@ -3002,10 +3071,10 @@
         <v>3.83</v>
       </c>
       <c r="AB23">
-        <v>0.9098</v>
+        <v>0.9138</v>
       </c>
       <c r="AC23" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD23">
         <v>0.2018</v>
@@ -3020,7 +3089,7 @@
         <v>0.2138</v>
       </c>
       <c r="AH23">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI23">
         <v>1.0084</v>
@@ -3029,10 +3098,10 @@
         <v>1</v>
       </c>
       <c r="AK23" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL23" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM23">
         <v>0</v>
@@ -3043,19 +3112,19 @@
         <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C24">
         <v>4.5</v>
       </c>
       <c r="D24">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E24">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="F24">
-        <v>5.86</v>
+        <v>5.89</v>
       </c>
       <c r="H24" t="s">
         <v>45</v>
@@ -3064,13 +3133,13 @@
         <v>45</v>
       </c>
       <c r="K24">
-        <v>5.86</v>
+        <v>5.89</v>
       </c>
       <c r="L24" t="s">
         <v>46</v>
       </c>
       <c r="M24" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="N24">
         <v>823913</v>
@@ -3115,10 +3184,10 @@
         <v>4.27</v>
       </c>
       <c r="AB24">
-        <v>1.2683</v>
+        <v>1.2739</v>
       </c>
       <c r="AC24" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD24">
         <v>0.2813</v>
@@ -3133,7 +3202,7 @@
         <v>0.2008</v>
       </c>
       <c r="AH24">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI24">
         <v>1.0004</v>
@@ -3142,10 +3211,10 @@
         <v>1</v>
       </c>
       <c r="AK24" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL24" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM24">
         <v>0</v>
@@ -3156,7 +3225,7 @@
         <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C25">
         <v>5.5</v>
@@ -3165,10 +3234,10 @@
         <v>128</v>
       </c>
       <c r="E25">
-        <v>-150</v>
+        <v>-155</v>
       </c>
       <c r="F25">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="H25" t="s">
         <v>45</v>
@@ -3177,13 +3246,13 @@
         <v>45</v>
       </c>
       <c r="K25">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="L25" t="s">
         <v>46</v>
       </c>
       <c r="M25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N25">
         <v>823185</v>
@@ -3228,10 +3297,10 @@
         <v>4.52</v>
       </c>
       <c r="AB25">
-        <v>0.9825</v>
+        <v>0.9868</v>
       </c>
       <c r="AC25" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD25">
         <v>0.2179</v>
@@ -3246,7 +3315,7 @@
         <v>0.2328</v>
       </c>
       <c r="AH25">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI25">
         <v>0.9642</v>
@@ -3255,10 +3324,10 @@
         <v>1</v>
       </c>
       <c r="AK25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL25" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM25">
         <v>0</v>
@@ -3269,19 +3338,19 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C26">
         <v>5.5</v>
       </c>
       <c r="D26">
-        <v>-130</v>
+        <v>-103</v>
       </c>
       <c r="E26">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="F26">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="H26" t="s">
         <v>45</v>
@@ -3290,13 +3359,13 @@
         <v>45</v>
       </c>
       <c r="K26">
-        <v>5.03</v>
+        <v>5.05</v>
       </c>
       <c r="L26" t="s">
         <v>46</v>
       </c>
       <c r="M26" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N26">
         <v>823185</v>
@@ -3341,10 +3410,10 @@
         <v>4.22</v>
       </c>
       <c r="AB26">
-        <v>1.0221</v>
+        <v>1.0266</v>
       </c>
       <c r="AC26" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD26">
         <v>0.2267</v>
@@ -3359,7 +3428,7 @@
         <v>0.2163</v>
       </c>
       <c r="AH26">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI26">
         <v>1.0197</v>
@@ -3368,10 +3437,10 @@
         <v>1</v>
       </c>
       <c r="AK26" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL26" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM26">
         <v>0</v>
@@ -3382,10 +3451,10 @@
         <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F27">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="s">
         <v>45</v>
@@ -3394,19 +3463,19 @@
         <v>45</v>
       </c>
       <c r="K27">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="L27" t="s">
         <v>46</v>
       </c>
       <c r="M27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N27">
         <v>824237</v>
       </c>
       <c r="O27" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P27">
         <v>3</v>
@@ -3445,10 +3514,10 @@
         <v>4.09</v>
       </c>
       <c r="AB27">
-        <v>0.844</v>
+        <v>0.8477</v>
       </c>
       <c r="AC27" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD27">
         <v>0.1872</v>
@@ -3463,7 +3532,7 @@
         <v>0.2262</v>
       </c>
       <c r="AH27">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI27">
         <v>0.9574</v>
@@ -3472,10 +3541,10 @@
         <v>1</v>
       </c>
       <c r="AK27" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL27" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM27">
         <v>0</v>
@@ -3486,10 +3555,10 @@
         <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F28">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
@@ -3498,13 +3567,13 @@
         <v>45</v>
       </c>
       <c r="K28">
-        <v>4.42</v>
+        <v>4.44</v>
       </c>
       <c r="L28" t="s">
         <v>46</v>
       </c>
       <c r="M28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N28">
         <v>822942</v>
@@ -3549,10 +3618,10 @@
         <v>4.23</v>
       </c>
       <c r="AB28">
-        <v>1.3442</v>
+        <v>1.3501</v>
       </c>
       <c r="AC28" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="AD28">
         <v>0.2982</v>
@@ -3567,7 +3636,7 @@
         <v>0.257</v>
       </c>
       <c r="AH28">
-        <v>0.2218</v>
+        <v>0.2208</v>
       </c>
       <c r="AI28">
         <v>1.0261</v>
@@ -3576,10 +3645,10 @@
         <v>1</v>
       </c>
       <c r="AK28" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AL28" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="AM28">
         <v>0</v>

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="94">
   <si>
     <t>date</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Landen Roupp</t>
+  </si>
+  <si>
+    <t>Jackson Jobe</t>
   </si>
 </sst>
 </file>
@@ -670,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="43" width="16" customWidth="1"/>
@@ -814,6 +817,15 @@
       <c r="B2" t="s">
         <v>44</v>
       </c>
+      <c r="C2">
+        <v>4.5</v>
+      </c>
+      <c r="D2">
+        <v>107</v>
+      </c>
+      <c r="E2">
+        <v>-120</v>
+      </c>
       <c r="F2">
         <v>4.93</v>
       </c>
@@ -848,7 +860,7 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T2">
         <v>0.22</v>
@@ -918,6 +930,15 @@
       <c r="B3" t="s">
         <v>51</v>
       </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+      <c r="D3">
+        <v>-138</v>
+      </c>
+      <c r="E3">
+        <v>121</v>
+      </c>
       <c r="F3">
         <v>4</v>
       </c>
@@ -952,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T3">
         <v>0.1974</v>
@@ -1022,6 +1043,15 @@
       <c r="B4" t="s">
         <v>52</v>
       </c>
+      <c r="C4">
+        <v>5.5</v>
+      </c>
+      <c r="D4">
+        <v>-128</v>
+      </c>
+      <c r="E4">
+        <v>102</v>
+      </c>
       <c r="F4">
         <v>7.22</v>
       </c>
@@ -1056,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>0.1899</v>
@@ -1126,6 +1156,15 @@
       <c r="B5" t="s">
         <v>55</v>
       </c>
+      <c r="C5">
+        <v>6.5</v>
+      </c>
+      <c r="D5">
+        <v>-106</v>
+      </c>
+      <c r="E5">
+        <v>-115</v>
+      </c>
       <c r="F5">
         <v>6.42</v>
       </c>
@@ -1160,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>0.2849</v>
@@ -1230,6 +1269,15 @@
       <c r="B6" t="s">
         <v>59</v>
       </c>
+      <c r="C6">
+        <v>4.5</v>
+      </c>
+      <c r="D6">
+        <v>118</v>
+      </c>
+      <c r="E6">
+        <v>-146</v>
+      </c>
       <c r="F6">
         <v>4</v>
       </c>
@@ -1264,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>0.1803</v>
@@ -1334,6 +1382,15 @@
       <c r="B7" t="s">
         <v>61</v>
       </c>
+      <c r="C7">
+        <v>4.5</v>
+      </c>
+      <c r="D7">
+        <v>120</v>
+      </c>
+      <c r="E7">
+        <v>-146</v>
+      </c>
       <c r="F7">
         <v>3.84</v>
       </c>
@@ -1368,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>0.2028</v>
@@ -1646,6 +1703,15 @@
       <c r="B10" t="s">
         <v>67</v>
       </c>
+      <c r="C10">
+        <v>3.5</v>
+      </c>
+      <c r="D10">
+        <v>-162</v>
+      </c>
+      <c r="E10">
+        <v>132</v>
+      </c>
       <c r="F10">
         <v>4.86</v>
       </c>
@@ -1680,7 +1746,7 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>0.2147</v>
@@ -1750,6 +1816,15 @@
       <c r="B11" t="s">
         <v>69</v>
       </c>
+      <c r="C11">
+        <v>7.5</v>
+      </c>
+      <c r="D11">
+        <v>125</v>
+      </c>
+      <c r="E11">
+        <v>-155</v>
+      </c>
       <c r="F11">
         <v>5.88</v>
       </c>
@@ -1784,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>0.3229</v>
@@ -1854,6 +1929,15 @@
       <c r="B12" t="s">
         <v>70</v>
       </c>
+      <c r="C12">
+        <v>2.5</v>
+      </c>
+      <c r="D12">
+        <v>-179</v>
+      </c>
+      <c r="E12">
+        <v>145</v>
+      </c>
       <c r="F12">
         <v>2.29</v>
       </c>
@@ -1888,7 +1972,7 @@
         <v>0</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T12">
         <v>0.1418</v>
@@ -3405,6 +3489,56 @@
       </c>
       <c r="AM26">
         <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>93</v>
+      </c>
+      <c r="C27">
+        <v>4.5</v>
+      </c>
+      <c r="D27">
+        <v>-110</v>
+      </c>
+      <c r="E27">
+        <v>-101</v>
+      </c>
+      <c r="H27" t="s">
+        <v>45</v>
+      </c>
+      <c r="J27" t="s">
+        <v>45</v>
+      </c>
+      <c r="L27" t="s">
+        <v>45</v>
+      </c>
+      <c r="M27" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" t="s">
+        <v>45</v>
+      </c>
+      <c r="O27" t="s">
+        <v>45</v>
+      </c>
+      <c r="S27">
+        <v>6</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AK27" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL27" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="88">
   <si>
     <t>date</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>league_lineup_k</t>
+  </si>
+  <si>
+    <t>whiff_leverage</t>
   </si>
   <si>
     <t>actual_k</t>
@@ -652,13 +655,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL27"/>
+  <dimension ref="A1:AM27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="38" width="16" customWidth="1"/>
+    <col min="1" max="39" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -772,14 +775,17 @@
       </c>
       <c r="AL1" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2">
         <v>4.5</v>
@@ -791,16 +797,16 @@
         <v>-120</v>
       </c>
       <c r="F2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G2">
         <v>824643</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -812,25 +818,25 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.22</v>
+        <v>0.2183</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="P2">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="Q2">
-        <v>0.2545</v>
+        <v>0.2418</v>
       </c>
       <c r="R2">
-        <v>0.355</v>
+        <v>0.313</v>
       </c>
       <c r="S2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T2">
         <v>0.2231</v>
@@ -842,25 +848,25 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2181</v>
+        <v>0.2178</v>
       </c>
       <c r="X2">
         <v>0.2229</v>
       </c>
       <c r="Z2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC2">
-        <v>4.93</v>
+        <v>4.62</v>
       </c>
       <c r="AD2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE2">
-        <v>0.2323</v>
+        <v>0.2256</v>
       </c>
       <c r="AF2">
         <v>1.0009</v>
@@ -869,15 +875,15 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>4.93</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>3.5</v>
@@ -889,16 +895,16 @@
         <v>121</v>
       </c>
       <c r="F3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <v>824643</v>
       </c>
       <c r="H3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I3">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -910,25 +916,25 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1974</v>
+        <v>0.1967</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="P3">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="Q3">
-        <v>0.2389</v>
+        <v>0.2188</v>
       </c>
       <c r="R3">
-        <v>0.361</v>
+        <v>0.324</v>
       </c>
       <c r="S3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T3">
         <v>0.1857</v>
@@ -946,19 +952,19 @@
         <v>0.2229</v>
       </c>
       <c r="Z3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC3">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE3">
-        <v>0.2124</v>
+        <v>0.2038</v>
       </c>
       <c r="AF3">
         <v>0.833</v>
@@ -967,15 +973,15 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>4</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4">
         <v>5.5</v>
@@ -987,13 +993,13 @@
         <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>824479</v>
       </c>
       <c r="H4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I4">
         <v>6.5</v>
@@ -1026,7 +1032,7 @@
         <v>0.396</v>
       </c>
       <c r="S4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T4">
         <v>0.3131</v>
@@ -1044,16 +1050,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC4">
         <v>8.02</v>
       </c>
       <c r="AD4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AE4">
         <v>0.1993</v>
@@ -1070,10 +1076,10 @@
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>6.5</v>
@@ -1085,13 +1091,13 @@
         <v>-115</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5">
         <v>824479</v>
       </c>
       <c r="H5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I5">
         <v>5.6</v>
@@ -1124,7 +1130,7 @@
         <v>0.359</v>
       </c>
       <c r="S5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T5">
         <v>0.2416</v>
@@ -1142,16 +1148,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC5">
         <v>6.42</v>
       </c>
       <c r="AD5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AE5">
         <v>0.2691</v>
@@ -1168,10 +1174,10 @@
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1183,13 +1189,13 @@
         <v>-146</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>823346</v>
       </c>
       <c r="H6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I6">
         <v>5.9</v>
@@ -1222,7 +1228,7 @@
         <v>0.381</v>
       </c>
       <c r="S6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T6">
         <v>0.2172</v>
@@ -1240,16 +1246,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC6">
         <v>4</v>
       </c>
       <c r="AD6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE6">
         <v>0.1736</v>
@@ -1266,10 +1272,10 @@
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1281,13 +1287,13 @@
         <v>-146</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>823346</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I7">
         <v>5</v>
@@ -1320,7 +1326,7 @@
         <v>0.351</v>
       </c>
       <c r="S7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T7">
         <v>0.1879</v>
@@ -1338,16 +1344,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC7">
         <v>3.84</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE7">
         <v>0.2096</v>
@@ -1364,19 +1370,19 @@
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>824237</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -1409,7 +1415,7 @@
         <v>0.043</v>
       </c>
       <c r="S8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T8">
         <v>0.1872</v>
@@ -1427,16 +1433,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC8">
         <v>2.34</v>
       </c>
       <c r="AD8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE8">
         <v>0.2375</v>
@@ -1453,19 +1459,19 @@
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G9">
         <v>823591</v>
       </c>
       <c r="H9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9">
         <v>4.7</v>
@@ -1498,7 +1504,7 @@
         <v>0.359</v>
       </c>
       <c r="S9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T9">
         <v>0.2518</v>
@@ -1516,16 +1522,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC9">
         <v>4.41</v>
       </c>
       <c r="AD9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE9">
         <v>0.1953</v>
@@ -1542,10 +1548,10 @@
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1557,13 +1563,13 @@
         <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>824399</v>
       </c>
       <c r="H10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I10">
         <v>5.7</v>
@@ -1596,7 +1602,7 @@
         <v>0.367</v>
       </c>
       <c r="S10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T10">
         <v>0.2156</v>
@@ -1614,16 +1620,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC10">
         <v>4.86</v>
       </c>
       <c r="AD10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE10">
         <v>0.2245</v>
@@ -1640,10 +1646,10 @@
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>7.5</v>
@@ -1655,13 +1661,13 @@
         <v>-155</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
         <v>824399</v>
       </c>
       <c r="H11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1694,7 +1700,7 @@
         <v>0.361</v>
       </c>
       <c r="S11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T11">
         <v>0.1504</v>
@@ -1712,16 +1718,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC11">
         <v>5.88</v>
       </c>
       <c r="AD11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE11">
         <v>0.3692</v>
@@ -1738,10 +1744,10 @@
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1753,13 +1759,13 @@
         <v>145</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>822942</v>
       </c>
       <c r="H12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I12">
         <v>4.6</v>
@@ -1792,7 +1798,7 @@
         <v>0.355</v>
       </c>
       <c r="S12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T12">
         <v>0.1813</v>
@@ -1810,16 +1816,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC12">
         <v>2.29</v>
       </c>
       <c r="AD12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE12">
         <v>0.1463</v>
@@ -1836,19 +1842,19 @@
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
+        <v>66</v>
+      </c>
+      <c r="F13" t="s">
         <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
       </c>
       <c r="G13">
         <v>822942</v>
       </c>
       <c r="H13" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13">
         <v>4.6</v>
@@ -1881,7 +1887,7 @@
         <v>0.317</v>
       </c>
       <c r="S13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T13">
         <v>0.2982</v>
@@ -1899,16 +1905,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC13">
         <v>4.39</v>
       </c>
       <c r="AD13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE13">
         <v>0.1646</v>
@@ -1925,19 +1931,19 @@
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>824882</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I14">
         <v>5.8</v>
@@ -1970,7 +1976,7 @@
         <v>0.385</v>
       </c>
       <c r="S14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T14">
         <v>0.2276</v>
@@ -1988,16 +1994,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC14">
         <v>3.25</v>
       </c>
       <c r="AD14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE14">
         <v>0.1333</v>
@@ -2014,19 +2020,19 @@
     </row>
     <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
         <v>68</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
       </c>
       <c r="G15">
         <v>824882</v>
       </c>
       <c r="H15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I15">
         <v>5.9</v>
@@ -2059,7 +2065,7 @@
         <v>0.338</v>
       </c>
       <c r="S15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T15">
         <v>0.1703</v>
@@ -2077,16 +2083,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC15">
         <v>5.4</v>
       </c>
       <c r="AD15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE15">
         <v>0.3316</v>
@@ -2103,19 +2109,19 @@
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16">
         <v>822777</v>
       </c>
       <c r="H16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I16">
         <v>5.8</v>
@@ -2148,7 +2154,7 @@
         <v>0.379</v>
       </c>
       <c r="S16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T16">
         <v>0.1919</v>
@@ -2166,16 +2172,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC16">
         <v>5.68</v>
       </c>
       <c r="AD16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE16">
         <v>0.2885</v>
@@ -2192,19 +2198,19 @@
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" t="s">
         <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
       </c>
       <c r="G17">
         <v>822777</v>
       </c>
       <c r="H17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I17">
         <v>4.7</v>
@@ -2237,7 +2243,7 @@
         <v>0.353</v>
       </c>
       <c r="S17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T17">
         <v>0.2757</v>
@@ -2255,16 +2261,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC17">
         <v>4.51</v>
       </c>
       <c r="AD17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE17">
         <v>0.1677</v>
@@ -2281,19 +2287,19 @@
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G18">
         <v>824159</v>
       </c>
       <c r="H18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I18">
         <v>6</v>
@@ -2326,7 +2332,7 @@
         <v>0.357</v>
       </c>
       <c r="S18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T18">
         <v>0.2132</v>
@@ -2344,16 +2350,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC18">
         <v>4.77</v>
       </c>
       <c r="AD18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE18">
         <v>0.2002</v>
@@ -2370,19 +2376,19 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
         <v>74</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
       </c>
       <c r="G19">
         <v>824159</v>
       </c>
       <c r="H19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I19">
         <v>5.7</v>
@@ -2415,7 +2421,7 @@
         <v>0.371</v>
       </c>
       <c r="S19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T19">
         <v>0.1987</v>
@@ -2433,16 +2439,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC19">
         <v>5.03</v>
       </c>
       <c r="AD19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE19">
         <v>0.2422</v>
@@ -2459,19 +2465,19 @@
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20">
         <v>823993</v>
       </c>
       <c r="H20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I20">
         <v>5.6</v>
@@ -2504,7 +2510,7 @@
         <v>0.379</v>
       </c>
       <c r="S20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T20">
         <v>0.2703</v>
@@ -2522,16 +2528,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC20">
         <v>5.04</v>
       </c>
       <c r="AD20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE20">
         <v>0.1688</v>
@@ -2548,19 +2554,19 @@
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" t="s">
         <v>77</v>
-      </c>
-      <c r="F21" t="s">
-        <v>76</v>
       </c>
       <c r="G21">
         <v>823993</v>
       </c>
       <c r="H21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I21">
         <v>4.6</v>
@@ -2593,7 +2599,7 @@
         <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T21">
         <v>0.2016</v>
@@ -2611,16 +2617,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC21">
         <v>3.87</v>
       </c>
       <c r="AD21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE21">
         <v>0.2122</v>
@@ -2637,19 +2643,19 @@
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
         <v>824968</v>
       </c>
       <c r="H22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I22">
         <v>4.9</v>
@@ -2682,7 +2688,7 @@
         <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T22">
         <v>0.2603</v>
@@ -2700,16 +2706,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC22">
         <v>5.67</v>
       </c>
       <c r="AD22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE22">
         <v>0.2252</v>
@@ -2726,19 +2732,19 @@
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G23">
         <v>823913</v>
       </c>
       <c r="H23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I23">
         <v>5.2</v>
@@ -2771,7 +2777,7 @@
         <v>0.34</v>
       </c>
       <c r="S23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T23">
         <v>0.2813</v>
@@ -2789,16 +2795,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC23">
         <v>5.84</v>
       </c>
       <c r="AD23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE23">
         <v>0.2101</v>
@@ -2815,19 +2821,19 @@
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
-      </c>
-      <c r="F24" t="s">
-        <v>81</v>
       </c>
       <c r="G24">
         <v>823913</v>
       </c>
       <c r="H24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I24">
         <v>6.6</v>
@@ -2860,7 +2866,7 @@
         <v>0.403</v>
       </c>
       <c r="S24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T24">
         <v>0.2018</v>
@@ -2878,16 +2884,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB24" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC24">
         <v>5.16</v>
       </c>
       <c r="AD24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE24">
         <v>0.2229</v>
@@ -2904,19 +2910,19 @@
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25">
         <v>823185</v>
       </c>
       <c r="H25" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I25">
         <v>5.4</v>
@@ -2949,7 +2955,7 @@
         <v>0.396</v>
       </c>
       <c r="S25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T25">
         <v>0.2179</v>
@@ -2967,16 +2973,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC25">
         <v>4.4</v>
       </c>
       <c r="AD25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE25">
         <v>0.1925</v>
@@ -2993,19 +2999,19 @@
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F26" t="s">
         <v>85</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
       </c>
       <c r="G26">
         <v>823185</v>
       </c>
       <c r="H26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I26">
         <v>5.4</v>
@@ -3038,7 +3044,7 @@
         <v>0.357</v>
       </c>
       <c r="S26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="T26">
         <v>0.2267</v>
@@ -3056,16 +3062,16 @@
         <v>0.2229</v>
       </c>
       <c r="Z26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC26">
         <v>5</v>
       </c>
       <c r="AD26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE26">
         <v>0.2126</v>
@@ -3082,10 +3088,10 @@
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3097,31 +3103,31 @@
         <v>-101</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Z27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AB27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AD27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -780,7 +780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2183</v>
+        <v>0.2194</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="P2">
-        <v>4.38</v>
+        <v>4.37</v>
       </c>
       <c r="Q2">
-        <v>0.2418</v>
+        <v>0.2447</v>
       </c>
       <c r="R2">
-        <v>0.313</v>
+        <v>0.32</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -848,37 +848,40 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2178</v>
+        <v>0.2179</v>
       </c>
       <c r="X2">
-        <v>0.2229</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC2">
-        <v>4.62</v>
-      </c>
-      <c r="AD2" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y2">
+        <v>0.975</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD2">
+        <v>4.67</v>
+      </c>
+      <c r="AE2" t="s">
         <v>45</v>
       </c>
-      <c r="AE2">
-        <v>0.2256</v>
-      </c>
       <c r="AF2">
-        <v>1.0009</v>
+        <v>0.2275</v>
       </c>
       <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>4.62</v>
+        <v>0.9988</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AM2">
+        <v>4.67</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -904,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -916,22 +919,22 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1967</v>
+        <v>0.1992</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="P3">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="Q3">
-        <v>0.2188</v>
+        <v>0.2323</v>
       </c>
       <c r="R3">
-        <v>0.324</v>
+        <v>0.331</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -946,37 +949,40 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2128</v>
+        <v>0.2127</v>
       </c>
       <c r="X3">
-        <v>0.2229</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC3">
-        <v>3.58</v>
-      </c>
-      <c r="AD3" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y3">
+        <v>0.9708</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD3">
+        <v>3.72</v>
+      </c>
+      <c r="AE3" t="s">
         <v>45</v>
       </c>
-      <c r="AE3">
-        <v>0.2038</v>
-      </c>
       <c r="AF3">
-        <v>0.833</v>
+        <v>0.2101</v>
       </c>
       <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>3.58</v>
+        <v>0.8313</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>3.72</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1047,34 +1053,37 @@
         <v>0.2548</v>
       </c>
       <c r="X4">
-        <v>0.2229</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC4">
-        <v>8.02</v>
-      </c>
-      <c r="AD4" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y4">
+        <v>1.062</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD4">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="s">
         <v>49</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>0.1993</v>
       </c>
-      <c r="AF4">
-        <v>1.4045</v>
-      </c>
       <c r="AG4">
+        <v>1.4015</v>
+      </c>
+      <c r="AH4">
         <v>-0.8</v>
       </c>
-      <c r="AL4">
-        <v>7.22</v>
+      <c r="AM4">
+        <v>7.2</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1145,34 +1154,37 @@
         <v>0.2108</v>
       </c>
       <c r="X5">
-        <v>0.2229</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC5">
-        <v>6.42</v>
-      </c>
-      <c r="AD5" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y5">
+        <v>0.9639</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD5">
+        <v>6.4</v>
+      </c>
+      <c r="AE5" t="s">
         <v>52</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>0.2691</v>
       </c>
-      <c r="AF5">
-        <v>1.0839</v>
-      </c>
       <c r="AG5">
-        <v>0</v>
-      </c>
-      <c r="AL5">
-        <v>6.42</v>
+        <v>1.0816</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>6.4</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -1243,34 +1255,37 @@
         <v>0.2568</v>
       </c>
       <c r="X6">
-        <v>0.2229</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC6">
-        <v>4</v>
-      </c>
-      <c r="AD6" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y6">
+        <v>1.0072</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD6">
+        <v>3.99</v>
+      </c>
+      <c r="AE6" t="s">
         <v>45</v>
       </c>
-      <c r="AE6">
+      <c r="AF6">
         <v>0.1736</v>
       </c>
-      <c r="AF6">
-        <v>0.9744</v>
-      </c>
       <c r="AG6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>4</v>
+        <v>0.9723</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>3.99</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1341,34 +1356,37 @@
         <v>0.2165</v>
       </c>
       <c r="X7">
-        <v>0.2229</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB7" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC7">
-        <v>3.84</v>
-      </c>
-      <c r="AD7" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y7">
+        <v>0.9858</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD7">
+        <v>3.83</v>
+      </c>
+      <c r="AE7" t="s">
         <v>45</v>
       </c>
-      <c r="AE7">
+      <c r="AF7">
         <v>0.2096</v>
       </c>
-      <c r="AF7">
-        <v>0.8428</v>
-      </c>
       <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>3.84</v>
+        <v>0.841</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>3.83</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -1415,13 +1433,13 @@
         <v>0.043</v>
       </c>
       <c r="S8" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.1872</v>
+        <v>0.2003</v>
       </c>
       <c r="U8">
-        <v>0.1956</v>
+        <v>0.1963</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1430,34 +1448,37 @@
         <v>0.2262</v>
       </c>
       <c r="X8">
-        <v>0.2229</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC8">
-        <v>2.34</v>
-      </c>
-      <c r="AD8" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y8">
+        <v>0.88</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD8">
+        <v>2.3</v>
+      </c>
+      <c r="AE8" t="s">
         <v>45</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>0.2375</v>
       </c>
-      <c r="AF8">
-        <v>0.8398</v>
-      </c>
       <c r="AG8">
-        <v>0</v>
-      </c>
-      <c r="AL8">
-        <v>2.34</v>
+        <v>0.8968</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>2.3</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -1519,34 +1540,37 @@
         <v>0.2293</v>
       </c>
       <c r="X9">
-        <v>0.2229</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC9">
-        <v>4.41</v>
-      </c>
-      <c r="AD9" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y9">
+        <v>0.989</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD9">
+        <v>4.4</v>
+      </c>
+      <c r="AE9" t="s">
         <v>45</v>
       </c>
-      <c r="AE9">
+      <c r="AF9">
         <v>0.1953</v>
       </c>
-      <c r="AF9">
-        <v>1.1293</v>
-      </c>
       <c r="AG9">
-        <v>0</v>
-      </c>
-      <c r="AL9">
-        <v>4.41</v>
+        <v>1.1269</v>
+      </c>
+      <c r="AH9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>4.4</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1617,34 +1641,37 @@
         <v>0.2141</v>
       </c>
       <c r="X10">
-        <v>0.2229</v>
-      </c>
-      <c r="Z10" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB10" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC10">
-        <v>4.86</v>
-      </c>
-      <c r="AD10" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y10">
+        <v>0.9615</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD10">
+        <v>4.85</v>
+      </c>
+      <c r="AE10" t="s">
         <v>45</v>
       </c>
-      <c r="AE10">
+      <c r="AF10">
         <v>0.2245</v>
       </c>
-      <c r="AF10">
-        <v>0.967</v>
-      </c>
       <c r="AG10">
-        <v>0</v>
-      </c>
-      <c r="AL10">
-        <v>4.86</v>
+        <v>0.9649</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>4.85</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1715,34 +1742,37 @@
         <v>0.2186</v>
       </c>
       <c r="X11">
-        <v>0.2229</v>
-      </c>
-      <c r="Z11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB11" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC11">
-        <v>5.88</v>
-      </c>
-      <c r="AD11" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y11">
+        <v>0.9884</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD11">
+        <v>5.87</v>
+      </c>
+      <c r="AE11" t="s">
         <v>45</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>0.3692</v>
       </c>
-      <c r="AF11">
-        <v>0.6748</v>
-      </c>
       <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>5.88</v>
+        <v>0.6734</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>5.87</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1813,34 +1843,37 @@
         <v>0.1905</v>
       </c>
       <c r="X12">
-        <v>0.2229</v>
-      </c>
-      <c r="Z12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC12">
+        <v>0.2234</v>
+      </c>
+      <c r="Y12">
+        <v>0.9044</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD12">
         <v>2.29</v>
       </c>
-      <c r="AD12" t="s">
+      <c r="AE12" t="s">
         <v>45</v>
       </c>
-      <c r="AE12">
+      <c r="AF12">
         <v>0.1463</v>
       </c>
-      <c r="AF12">
-        <v>0.8134</v>
-      </c>
       <c r="AG12">
-        <v>0</v>
-      </c>
-      <c r="AL12">
+        <v>0.8117</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
         <v>2.29</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1902,34 +1935,37 @@
         <v>0.257</v>
       </c>
       <c r="X13">
-        <v>0.2229</v>
-      </c>
-      <c r="Z13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC13">
-        <v>4.39</v>
-      </c>
-      <c r="AD13" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y13">
+        <v>1.0261</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD13">
+        <v>4.38</v>
+      </c>
+      <c r="AE13" t="s">
         <v>45</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>0.1646</v>
       </c>
-      <c r="AF13">
-        <v>1.3374</v>
-      </c>
       <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>4.39</v>
+        <v>1.3346</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>4.38</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1991,34 +2027,37 @@
         <v>0.2174</v>
       </c>
       <c r="X14">
-        <v>0.2229</v>
-      </c>
-      <c r="Z14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC14">
-        <v>3.25</v>
-      </c>
-      <c r="AD14" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y14">
+        <v>0.9816</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD14">
+        <v>3.24</v>
+      </c>
+      <c r="AE14" t="s">
         <v>45</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>0.1333</v>
       </c>
-      <c r="AF14">
-        <v>1.0211</v>
-      </c>
       <c r="AG14">
-        <v>0</v>
-      </c>
-      <c r="AL14">
-        <v>3.25</v>
+        <v>1.0189</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>3.24</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -2080,34 +2119,37 @@
         <v>0.1705</v>
       </c>
       <c r="X15">
-        <v>0.2229</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC15">
-        <v>5.4</v>
-      </c>
-      <c r="AD15" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y15">
+        <v>0.9069</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD15">
+        <v>5.39</v>
+      </c>
+      <c r="AE15" t="s">
         <v>45</v>
       </c>
-      <c r="AE15">
+      <c r="AF15">
         <v>0.3316</v>
       </c>
-      <c r="AF15">
-        <v>0.7641</v>
-      </c>
       <c r="AG15">
-        <v>0</v>
-      </c>
-      <c r="AL15">
-        <v>5.4</v>
+        <v>0.7624</v>
+      </c>
+      <c r="AH15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>5.39</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -2169,34 +2211,37 @@
         <v>0.1887</v>
       </c>
       <c r="X16">
-        <v>0.2229</v>
-      </c>
-      <c r="Z16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC16">
-        <v>5.68</v>
-      </c>
-      <c r="AD16" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y16">
+        <v>0.9732</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD16">
+        <v>5.67</v>
+      </c>
+      <c r="AE16" t="s">
         <v>45</v>
       </c>
-      <c r="AE16">
+      <c r="AF16">
         <v>0.2885</v>
       </c>
-      <c r="AF16">
-        <v>0.861</v>
-      </c>
       <c r="AG16">
-        <v>0</v>
-      </c>
-      <c r="AL16">
-        <v>5.68</v>
+        <v>0.8592</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>5.67</v>
       </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>39</v>
       </c>
@@ -2258,34 +2303,37 @@
         <v>0.2442</v>
       </c>
       <c r="X17">
-        <v>0.2229</v>
-      </c>
-      <c r="Z17" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB17" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC17">
-        <v>4.51</v>
-      </c>
-      <c r="AD17" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y17">
+        <v>1.0039</v>
+      </c>
+      <c r="AA17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD17">
+        <v>4.5</v>
+      </c>
+      <c r="AE17" t="s">
         <v>45</v>
       </c>
-      <c r="AE17">
+      <c r="AF17">
         <v>0.1677</v>
       </c>
-      <c r="AF17">
-        <v>1.2365</v>
-      </c>
       <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>4.51</v>
+        <v>1.2339</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>39</v>
       </c>
@@ -2347,34 +2395,37 @@
         <v>0.2162</v>
       </c>
       <c r="X18">
-        <v>0.2229</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB18" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC18">
-        <v>4.77</v>
-      </c>
-      <c r="AD18" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y18">
+        <v>1.0104</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD18">
+        <v>4.76</v>
+      </c>
+      <c r="AE18" t="s">
         <v>45</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>0.2002</v>
       </c>
-      <c r="AF18">
-        <v>0.9564</v>
-      </c>
       <c r="AG18">
-        <v>0</v>
-      </c>
-      <c r="AL18">
-        <v>4.77</v>
+        <v>0.9544</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>4.76</v>
       </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -2436,34 +2487,37 @@
         <v>0.2256</v>
       </c>
       <c r="X19">
-        <v>0.2229</v>
-      </c>
-      <c r="Z19" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC19">
-        <v>5.03</v>
-      </c>
-      <c r="AD19" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y19">
+        <v>0.9876</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD19">
+        <v>5.02</v>
+      </c>
+      <c r="AE19" t="s">
         <v>45</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>0.2422</v>
       </c>
-      <c r="AF19">
-        <v>0.8911</v>
-      </c>
       <c r="AG19">
-        <v>0</v>
-      </c>
-      <c r="AL19">
-        <v>5.03</v>
+        <v>0.8893</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>5.02</v>
       </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -2525,34 +2579,37 @@
         <v>0.2508</v>
       </c>
       <c r="X20">
-        <v>0.2229</v>
-      </c>
-      <c r="Z20" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC20">
-        <v>5.04</v>
-      </c>
-      <c r="AD20" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y20">
+        <v>1.0327</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD20">
+        <v>5.03</v>
+      </c>
+      <c r="AE20" t="s">
         <v>45</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>0.1688</v>
       </c>
-      <c r="AF20">
-        <v>1.2123</v>
-      </c>
       <c r="AG20">
-        <v>0</v>
-      </c>
-      <c r="AL20">
-        <v>5.04</v>
+        <v>1.2097</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>5.03</v>
       </c>
     </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -2614,34 +2671,37 @@
         <v>0.2092</v>
       </c>
       <c r="X21">
-        <v>0.2229</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB21" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC21">
-        <v>3.87</v>
-      </c>
-      <c r="AD21" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y21">
+        <v>0.9531</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD21">
+        <v>3.86</v>
+      </c>
+      <c r="AE21" t="s">
         <v>45</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>0.2122</v>
       </c>
-      <c r="AF21">
-        <v>0.9044</v>
-      </c>
       <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>3.87</v>
+        <v>0.9025</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>3.86</v>
       </c>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2703,34 +2763,37 @@
         <v>0.2168</v>
       </c>
       <c r="X22">
-        <v>0.2229</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB22" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC22">
-        <v>5.67</v>
-      </c>
-      <c r="AD22" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y22">
+        <v>1.013</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD22">
+        <v>5.66</v>
+      </c>
+      <c r="AE22" t="s">
         <v>45</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>0.2252</v>
       </c>
-      <c r="AF22">
-        <v>1.1675</v>
-      </c>
       <c r="AG22">
-        <v>0</v>
-      </c>
-      <c r="AL22">
-        <v>5.67</v>
+        <v>1.1651</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>5.66</v>
       </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -2792,34 +2855,37 @@
         <v>0.2008</v>
       </c>
       <c r="X23">
-        <v>0.2229</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB23" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC23">
-        <v>5.84</v>
-      </c>
-      <c r="AD23" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y23">
+        <v>1.0004</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD23">
+        <v>5.82</v>
+      </c>
+      <c r="AE23" t="s">
         <v>45</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>0.2101</v>
       </c>
-      <c r="AF23">
-        <v>1.262</v>
-      </c>
       <c r="AG23">
-        <v>0</v>
-      </c>
-      <c r="AL23">
-        <v>5.84</v>
+        <v>1.2593</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>5.82</v>
       </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -2881,34 +2947,37 @@
         <v>0.2138</v>
       </c>
       <c r="X24">
+        <v>0.2234</v>
+      </c>
+      <c r="Y24">
+        <v>1.0084</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD24">
+        <v>5.15</v>
+      </c>
+      <c r="AE24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF24">
         <v>0.2229</v>
       </c>
-      <c r="Z24" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB24" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC24">
-        <v>5.16</v>
-      </c>
-      <c r="AD24" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE24">
-        <v>0.2229</v>
-      </c>
-      <c r="AF24">
-        <v>0.9052</v>
-      </c>
       <c r="AG24">
-        <v>0</v>
-      </c>
-      <c r="AL24">
-        <v>5.16</v>
+        <v>0.9033</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>5.15</v>
       </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>39</v>
       </c>
@@ -2970,34 +3039,37 @@
         <v>0.2328</v>
       </c>
       <c r="X25">
-        <v>0.2229</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC25">
-        <v>4.4</v>
-      </c>
-      <c r="AD25" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y25">
+        <v>0.9642</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD25">
+        <v>4.39</v>
+      </c>
+      <c r="AE25" t="s">
         <v>45</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>0.1925</v>
       </c>
-      <c r="AF25">
-        <v>0.9776</v>
-      </c>
       <c r="AG25">
-        <v>0</v>
-      </c>
-      <c r="AL25">
-        <v>4.4</v>
+        <v>0.9756</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>4.39</v>
       </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3059,34 +3131,37 @@
         <v>0.2163</v>
       </c>
       <c r="X26">
-        <v>0.2229</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC26">
-        <v>5</v>
-      </c>
-      <c r="AD26" t="s">
+        <v>0.2234</v>
+      </c>
+      <c r="Y26">
+        <v>1.0197</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD26">
+        <v>4.99</v>
+      </c>
+      <c r="AE26" t="s">
         <v>45</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>0.2126</v>
       </c>
-      <c r="AF26">
-        <v>1.017</v>
-      </c>
       <c r="AG26">
-        <v>0</v>
-      </c>
-      <c r="AL26">
-        <v>5</v>
+        <v>1.0149</v>
+      </c>
+      <c r="AH26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>4.99</v>
       </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3120,13 +3195,13 @@
       <c r="V27" t="s">
         <v>44</v>
       </c>
-      <c r="Z27" t="s">
-        <v>44</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>44</v>
-      </c>
-      <c r="AD27" t="s">
+      <c r="AA27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC27" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE27" t="s">
         <v>44</v>
       </c>
     </row>

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -806,7 +806,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2194</v>
+        <v>0.2207</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="P2">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="Q2">
-        <v>0.2447</v>
+        <v>0.25</v>
       </c>
       <c r="R2">
-        <v>0.32</v>
+        <v>0.333</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -848,10 +848,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2179</v>
+        <v>0.2184</v>
       </c>
       <c r="X2">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y2">
         <v>0.975</v>
@@ -863,22 +863,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.67</v>
+        <v>4.83</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2275</v>
+        <v>0.2305</v>
       </c>
       <c r="AG2">
-        <v>0.9988</v>
+        <v>1.0071</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.67</v>
+        <v>4.83</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -919,22 +919,22 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1992</v>
+        <v>0.1959</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="P3">
-        <v>4.06</v>
+        <v>4.04</v>
       </c>
       <c r="Q3">
-        <v>0.2323</v>
+        <v>0.2233</v>
       </c>
       <c r="R3">
-        <v>0.331</v>
+        <v>0.34</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -952,7 +952,7 @@
         <v>0.2127</v>
       </c>
       <c r="X3">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y3">
         <v>0.9708</v>
@@ -970,10 +970,10 @@
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2101</v>
+        <v>0.2052</v>
       </c>
       <c r="AG3">
-        <v>0.8313</v>
+        <v>0.8382</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1053,7 +1053,7 @@
         <v>0.2548</v>
       </c>
       <c r="X4">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y4">
         <v>1.062</v>
@@ -1065,7 +1065,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>8.07</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
@@ -1074,13 +1074,13 @@
         <v>0.1993</v>
       </c>
       <c r="AG4">
-        <v>1.4015</v>
+        <v>1.4131</v>
       </c>
       <c r="AH4">
         <v>-0.8</v>
       </c>
       <c r="AM4">
-        <v>7.2</v>
+        <v>7.27</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1154,7 +1154,7 @@
         <v>0.2108</v>
       </c>
       <c r="X5">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y5">
         <v>0.9639</v>
@@ -1166,7 +1166,7 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.4</v>
+        <v>6.46</v>
       </c>
       <c r="AE5" t="s">
         <v>52</v>
@@ -1175,13 +1175,13 @@
         <v>0.2691</v>
       </c>
       <c r="AG5">
-        <v>1.0816</v>
+        <v>1.0906</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.4</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1240,25 +1240,25 @@
         <v>0.381</v>
       </c>
       <c r="S6" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T6">
-        <v>0.2172</v>
+        <v>0.248</v>
       </c>
       <c r="U6">
-        <v>0.2403</v>
+        <v>0.2657</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>0.2568</v>
       </c>
       <c r="X6">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y6">
-        <v>1.0072</v>
+        <v>1.0839</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1267,7 +1267,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.99</v>
+        <v>4.94</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1276,13 +1276,13 @@
         <v>0.1736</v>
       </c>
       <c r="AG6">
-        <v>0.9723</v>
+        <v>1.1192</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.99</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1341,13 +1341,13 @@
         <v>0.351</v>
       </c>
       <c r="S7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T7">
-        <v>0.1879</v>
+        <v>0.1822</v>
       </c>
       <c r="U7">
-        <v>0.1859</v>
+        <v>0.1809</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1356,10 +1356,10 @@
         <v>0.2165</v>
       </c>
       <c r="X7">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y7">
-        <v>0.9858</v>
+        <v>0.9909</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1368,7 +1368,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1377,13 +1377,13 @@
         <v>0.2096</v>
       </c>
       <c r="AG7">
-        <v>0.841</v>
+        <v>0.8225</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1448,7 +1448,7 @@
         <v>0.2262</v>
       </c>
       <c r="X8">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y8">
         <v>0.88</v>
@@ -1460,7 +1460,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1469,13 +1469,13 @@
         <v>0.2375</v>
       </c>
       <c r="AG8">
-        <v>0.8968</v>
+        <v>0.9042</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1525,25 +1525,25 @@
         <v>0.359</v>
       </c>
       <c r="S9" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2518</v>
+        <v>0.2323</v>
       </c>
       <c r="U9">
-        <v>0.2481</v>
+        <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>0.2293</v>
       </c>
       <c r="X9">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y9">
-        <v>0.989</v>
+        <v>0.9762</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1552,7 +1552,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.4</v>
+        <v>4.04</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1561,13 +1561,13 @@
         <v>0.1953</v>
       </c>
       <c r="AG9">
-        <v>1.1269</v>
+        <v>1.0485</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.4</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1626,13 +1626,13 @@
         <v>0.367</v>
       </c>
       <c r="S10" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2156</v>
+        <v>0.1653</v>
       </c>
       <c r="U10">
-        <v>0.2003</v>
+        <v>0.17</v>
       </c>
       <c r="V10">
         <v>9</v>
@@ -1641,10 +1641,10 @@
         <v>0.2141</v>
       </c>
       <c r="X10">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y10">
-        <v>0.9615</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1653,7 +1653,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>4.85</v>
+        <v>3.43</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1662,13 +1662,13 @@
         <v>0.2245</v>
       </c>
       <c r="AG10">
-        <v>0.9649</v>
+        <v>0.746</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>4.85</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1742,7 +1742,7 @@
         <v>0.2186</v>
       </c>
       <c r="X11">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y11">
         <v>0.9884</v>
@@ -1754,7 +1754,7 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.87</v>
+        <v>5.92</v>
       </c>
       <c r="AE11" t="s">
         <v>45</v>
@@ -1763,13 +1763,13 @@
         <v>0.3692</v>
       </c>
       <c r="AG11">
-        <v>0.6734</v>
+        <v>0.679</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.87</v>
+        <v>5.92</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1828,13 +1828,13 @@
         <v>0.355</v>
       </c>
       <c r="S12" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1813</v>
+        <v>0.1871</v>
       </c>
       <c r="U12">
-        <v>0.1763</v>
+        <v>0.1808</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1843,10 +1843,10 @@
         <v>0.1905</v>
       </c>
       <c r="X12">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y12">
-        <v>0.9044</v>
+        <v>0.88</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1855,7 +1855,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1864,13 +1864,13 @@
         <v>0.1463</v>
       </c>
       <c r="AG12">
-        <v>0.8117</v>
+        <v>0.8445</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>0.257</v>
       </c>
       <c r="X13">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y13">
         <v>1.0261</v>
@@ -1947,7 +1947,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1956,13 +1956,13 @@
         <v>0.1646</v>
       </c>
       <c r="AG13">
-        <v>1.3346</v>
+        <v>1.3457</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.38</v>
+        <v>4.42</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2012,13 +2012,13 @@
         <v>0.385</v>
       </c>
       <c r="S14" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2276</v>
+        <v>0.2109</v>
       </c>
       <c r="U14">
-        <v>0.2209</v>
+        <v>0.2075</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -2027,10 +2027,10 @@
         <v>0.2174</v>
       </c>
       <c r="X14">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y14">
-        <v>0.9816</v>
+        <v>0.9698</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2039,7 +2039,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2048,13 +2048,13 @@
         <v>0.1333</v>
       </c>
       <c r="AG14">
-        <v>1.0189</v>
+        <v>0.9518</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2104,13 +2104,13 @@
         <v>0.338</v>
       </c>
       <c r="S15" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.1703</v>
+        <v>0.1745</v>
       </c>
       <c r="U15">
-        <v>0.1681</v>
+        <v>0.1721</v>
       </c>
       <c r="V15">
         <v>9</v>
@@ -2119,10 +2119,10 @@
         <v>0.1705</v>
       </c>
       <c r="X15">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y15">
-        <v>0.9069</v>
+        <v>0.88</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2131,7 +2131,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2140,13 +2140,13 @@
         <v>0.3316</v>
       </c>
       <c r="AG15">
-        <v>0.7624</v>
+        <v>0.7876</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.39</v>
+        <v>5.41</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>0.1887</v>
       </c>
       <c r="X16">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y16">
         <v>0.9732</v>
@@ -2223,7 +2223,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2232,13 +2232,13 @@
         <v>0.2885</v>
       </c>
       <c r="AG16">
-        <v>0.8592</v>
+        <v>0.8663</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.67</v>
+        <v>5.72</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2303,7 +2303,7 @@
         <v>0.2442</v>
       </c>
       <c r="X17">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y17">
         <v>1.0039</v>
@@ -2315,7 +2315,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2324,13 +2324,13 @@
         <v>0.1677</v>
       </c>
       <c r="AG17">
-        <v>1.2339</v>
+        <v>1.2441</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2395,7 +2395,7 @@
         <v>0.2162</v>
       </c>
       <c r="X18">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y18">
         <v>1.0104</v>
@@ -2407,7 +2407,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2416,13 +2416,13 @@
         <v>0.2002</v>
       </c>
       <c r="AG18">
-        <v>0.9544</v>
+        <v>0.9623</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2487,7 +2487,7 @@
         <v>0.2256</v>
       </c>
       <c r="X19">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y19">
         <v>0.9876</v>
@@ -2499,7 +2499,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2508,13 +2508,13 @@
         <v>0.2422</v>
       </c>
       <c r="AG19">
-        <v>0.8893</v>
+        <v>0.8966</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.02</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2579,7 +2579,7 @@
         <v>0.2508</v>
       </c>
       <c r="X20">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y20">
         <v>1.0327</v>
@@ -2591,7 +2591,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2600,13 +2600,13 @@
         <v>0.1688</v>
       </c>
       <c r="AG20">
-        <v>1.2097</v>
+        <v>1.2197</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.03</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2671,7 +2671,7 @@
         <v>0.2092</v>
       </c>
       <c r="X21">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y21">
         <v>0.9531</v>
@@ -2683,7 +2683,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2692,13 +2692,13 @@
         <v>0.2122</v>
       </c>
       <c r="AG21">
-        <v>0.9025</v>
+        <v>0.91</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2763,7 +2763,7 @@
         <v>0.2168</v>
       </c>
       <c r="X22">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y22">
         <v>1.013</v>
@@ -2775,7 +2775,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.66</v>
+        <v>5.71</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2784,13 +2784,13 @@
         <v>0.2252</v>
       </c>
       <c r="AG22">
-        <v>1.1651</v>
+        <v>1.1747</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.66</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2855,7 +2855,7 @@
         <v>0.2008</v>
       </c>
       <c r="X23">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y23">
         <v>1.0004</v>
@@ -2867,7 +2867,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.82</v>
+        <v>5.87</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2876,13 +2876,13 @@
         <v>0.2101</v>
       </c>
       <c r="AG23">
-        <v>1.2593</v>
+        <v>1.2697</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.82</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2947,7 +2947,7 @@
         <v>0.2138</v>
       </c>
       <c r="X24">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y24">
         <v>1.0084</v>
@@ -2959,7 +2959,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.15</v>
+        <v>5.19</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -2968,13 +2968,13 @@
         <v>0.2229</v>
       </c>
       <c r="AG24">
-        <v>0.9033</v>
+        <v>0.9108</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.15</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3039,7 +3039,7 @@
         <v>0.2328</v>
       </c>
       <c r="X25">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y25">
         <v>0.9642</v>
@@ -3051,7 +3051,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3060,13 +3060,13 @@
         <v>0.1925</v>
       </c>
       <c r="AG25">
-        <v>0.9756</v>
+        <v>0.9836</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.39</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3131,7 +3131,7 @@
         <v>0.2163</v>
       </c>
       <c r="X26">
-        <v>0.2234</v>
+        <v>0.2216</v>
       </c>
       <c r="Y26">
         <v>1.0197</v>
@@ -3143,7 +3143,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>4.99</v>
+        <v>5.04</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3152,13 +3152,13 @@
         <v>0.2126</v>
       </c>
       <c r="AG26">
-        <v>1.0149</v>
+        <v>1.0233</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>4.99</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -166,94 +166,94 @@
     <t>Chase Burns</t>
   </si>
   <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Jake Bennett</t>
+  </si>
+  <si>
+    <t>Boston Red Sox @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Bubba Chandler</t>
+  </si>
+  <si>
+    <t>Sean Newcomb</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Detroit Tigers</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Andrew Alvarez</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ New York Mets</t>
+  </si>
+  <si>
+    <t>Michael King</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>Chris Bassitt</t>
+  </si>
+  <si>
+    <t>Baltimore Orioles @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Steven Matz</t>
+  </si>
+  <si>
+    <t>Brandon Pfaadt</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Atlanta Braves</t>
+  </si>
+  <si>
+    <t>Chris Sale</t>
+  </si>
+  <si>
+    <t>Gerrit Cole</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Toronto Blue Jays</t>
+  </si>
+  <si>
+    <t>Shane Bieber</t>
+  </si>
+  <si>
+    <t>George Kirby</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Peter Lambert</t>
+  </si>
+  <si>
+    <t>Seth Lugo</t>
+  </si>
+  <si>
+    <t>Kansas City Royals @ Los Angeles Angels</t>
+  </si>
+  <si>
+    <t>Grayson Rodriguez</t>
+  </si>
+  <si>
+    <t>Kumar Rocker</t>
+  </si>
+  <si>
+    <t>Texas Rangers @ Athletics</t>
+  </si>
+  <si>
     <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Jake Bennett</t>
-  </si>
-  <si>
-    <t>Boston Red Sox @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Bubba Chandler</t>
-  </si>
-  <si>
-    <t>Sean Newcomb</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Detroit Tigers</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Andrew Alvarez</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ New York Mets</t>
-  </si>
-  <si>
-    <t>Michael King</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Gavin Williams</t>
-  </si>
-  <si>
-    <t>Chris Bassitt</t>
-  </si>
-  <si>
-    <t>Baltimore Orioles @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Steven Matz</t>
-  </si>
-  <si>
-    <t>Brandon Pfaadt</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Atlanta Braves</t>
-  </si>
-  <si>
-    <t>Chris Sale</t>
-  </si>
-  <si>
-    <t>Gerrit Cole</t>
-  </si>
-  <si>
-    <t>New York Yankees @ Toronto Blue Jays</t>
-  </si>
-  <si>
-    <t>Shane Bieber</t>
-  </si>
-  <si>
-    <t>George Kirby</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Peter Lambert</t>
-  </si>
-  <si>
-    <t>Seth Lugo</t>
-  </si>
-  <si>
-    <t>Kansas City Royals @ Los Angeles Angels</t>
-  </si>
-  <si>
-    <t>Grayson Rodriguez</t>
-  </si>
-  <si>
-    <t>Kumar Rocker</t>
-  </si>
-  <si>
-    <t>Texas Rangers @ Athletics</t>
   </si>
   <si>
     <t>Robert Gasser</t>
@@ -806,7 +806,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -818,22 +818,22 @@
         <v>6</v>
       </c>
       <c r="M2">
-        <v>0.2207</v>
+        <v>0.2235</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P2">
-        <v>4.35</v>
+        <v>4.36</v>
       </c>
       <c r="Q2">
-        <v>0.25</v>
+        <v>0.2617</v>
       </c>
       <c r="R2">
-        <v>0.333</v>
+        <v>0.349</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
@@ -848,10 +848,10 @@
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2184</v>
+        <v>0.2195</v>
       </c>
       <c r="X2">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y2">
         <v>0.975</v>
@@ -863,22 +863,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>4.83</v>
+        <v>5.13</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2305</v>
+        <v>0.2368</v>
       </c>
       <c r="AG2">
-        <v>1.0071</v>
+        <v>1.0268</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>4.83</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,7 +907,7 @@
         <v>42</v>
       </c>
       <c r="I3">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="b">
         <v>0</v>
@@ -919,22 +919,22 @@
         <v>6</v>
       </c>
       <c r="M3">
-        <v>0.1959</v>
+        <v>0.1922</v>
       </c>
       <c r="N3">
         <v>5</v>
       </c>
       <c r="O3">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="P3">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="Q3">
-        <v>0.2233</v>
+        <v>0.2124</v>
       </c>
       <c r="R3">
-        <v>0.34</v>
+        <v>0.361</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
@@ -949,10 +949,10 @@
         <v>9</v>
       </c>
       <c r="W3">
-        <v>0.2127</v>
+        <v>0.2126</v>
       </c>
       <c r="X3">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y3">
         <v>0.9708</v>
@@ -964,22 +964,22 @@
         <v>44</v>
       </c>
       <c r="AD3">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="AE3" t="s">
         <v>45</v>
       </c>
       <c r="AF3">
-        <v>0.2052</v>
+        <v>0.1995</v>
       </c>
       <c r="AG3">
-        <v>0.8382</v>
+        <v>0.8546</v>
       </c>
       <c r="AH3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1053,7 +1053,7 @@
         <v>0.2548</v>
       </c>
       <c r="X4">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y4">
         <v>1.062</v>
@@ -1065,7 +1065,7 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>8.07</v>
+        <v>8.22</v>
       </c>
       <c r="AE4" t="s">
         <v>49</v>
@@ -1074,13 +1074,13 @@
         <v>0.1993</v>
       </c>
       <c r="AG4">
-        <v>1.4131</v>
+        <v>1.4408</v>
       </c>
       <c r="AH4">
         <v>-0.8</v>
       </c>
       <c r="AM4">
-        <v>7.27</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1139,13 +1139,13 @@
         <v>0.359</v>
       </c>
       <c r="S5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2416</v>
+        <v>0.2407</v>
       </c>
       <c r="U5">
-        <v>0.2329</v>
+        <v>0.2229</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -1154,10 +1154,10 @@
         <v>0.2108</v>
       </c>
       <c r="X5">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y5">
-        <v>0.9639</v>
+        <v>0.8833</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1166,22 +1166,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.46</v>
+        <v>6.01</v>
       </c>
       <c r="AE5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AF5">
         <v>0.2691</v>
       </c>
       <c r="AG5">
-        <v>1.0906</v>
+        <v>1.1076</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.46</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1189,7 +1189,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1201,7 +1201,7 @@
         <v>-146</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>823346</v>
@@ -1255,7 +1255,7 @@
         <v>0.2568</v>
       </c>
       <c r="X6">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y6">
         <v>1.0839</v>
@@ -1267,7 +1267,7 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>4.94</v>
+        <v>5.04</v>
       </c>
       <c r="AE6" t="s">
         <v>45</v>
@@ -1276,13 +1276,13 @@
         <v>0.1736</v>
       </c>
       <c r="AG6">
-        <v>1.1192</v>
+        <v>1.1412</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>4.94</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1290,7 +1290,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1302,7 +1302,7 @@
         <v>-146</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>823346</v>
@@ -1356,7 +1356,7 @@
         <v>0.2165</v>
       </c>
       <c r="X7">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y7">
         <v>0.9909</v>
@@ -1368,7 +1368,7 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AE7" t="s">
         <v>45</v>
@@ -1377,13 +1377,13 @@
         <v>0.2096</v>
       </c>
       <c r="AG7">
-        <v>0.8225</v>
+        <v>0.8387</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1391,16 +1391,16 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
         <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
       </c>
       <c r="G8">
         <v>824237</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -1448,7 +1448,7 @@
         <v>0.2262</v>
       </c>
       <c r="X8">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y8">
         <v>0.88</v>
@@ -1460,7 +1460,7 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AE8" t="s">
         <v>45</v>
@@ -1469,13 +1469,13 @@
         <v>0.2375</v>
       </c>
       <c r="AG8">
-        <v>0.9042</v>
+        <v>0.9219</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1483,10 +1483,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
         <v>59</v>
-      </c>
-      <c r="F9" t="s">
-        <v>60</v>
       </c>
       <c r="G9">
         <v>823591</v>
@@ -1540,7 +1540,7 @@
         <v>0.2293</v>
       </c>
       <c r="X9">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y9">
         <v>0.9762</v>
@@ -1552,7 +1552,7 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
       <c r="AE9" t="s">
         <v>45</v>
@@ -1561,13 +1561,13 @@
         <v>0.1953</v>
       </c>
       <c r="AG9">
-        <v>1.0485</v>
+        <v>1.0691</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.04</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1575,7 +1575,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1587,7 +1587,7 @@
         <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>824399</v>
@@ -1641,7 +1641,7 @@
         <v>0.2141</v>
       </c>
       <c r="X10">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y10">
         <v>0.88</v>
@@ -1653,7 +1653,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="AE10" t="s">
         <v>45</v>
@@ -1662,13 +1662,13 @@
         <v>0.2245</v>
       </c>
       <c r="AG10">
-        <v>0.746</v>
+        <v>0.7606</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1676,7 +1676,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11">
         <v>7.5</v>
@@ -1688,7 +1688,7 @@
         <v>-155</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
         <v>824399</v>
@@ -1727,13 +1727,13 @@
         <v>0.361</v>
       </c>
       <c r="S11" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T11">
-        <v>0.1504</v>
+        <v>0.169</v>
       </c>
       <c r="U11">
-        <v>0.1685</v>
+        <v>0.1711</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1742,10 +1742,10 @@
         <v>0.2186</v>
       </c>
       <c r="X11">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y11">
-        <v>0.9884</v>
+        <v>0.9878</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1754,22 +1754,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>5.92</v>
+        <v>6.77</v>
       </c>
       <c r="AE11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF11">
         <v>0.3692</v>
       </c>
       <c r="AG11">
-        <v>0.679</v>
+        <v>0.7775</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>5.92</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1777,7 +1777,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1789,7 +1789,7 @@
         <v>145</v>
       </c>
       <c r="F12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>822942</v>
@@ -1843,7 +1843,7 @@
         <v>0.1905</v>
       </c>
       <c r="X12">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y12">
         <v>0.88</v>
@@ -1855,7 +1855,7 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AE12" t="s">
         <v>45</v>
@@ -1864,13 +1864,13 @@
         <v>0.1463</v>
       </c>
       <c r="AG12">
-        <v>0.8445</v>
+        <v>0.8611</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1878,10 +1878,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13">
         <v>822942</v>
@@ -1920,25 +1920,25 @@
         <v>0.317</v>
       </c>
       <c r="S13" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2982</v>
+        <v>0.269</v>
       </c>
       <c r="U13">
-        <v>0.2664</v>
+        <v>0.2575</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>0.257</v>
       </c>
       <c r="X13">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y13">
-        <v>1.0261</v>
+        <v>1.0594</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1947,7 +1947,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="AE13" t="s">
         <v>45</v>
@@ -1956,13 +1956,13 @@
         <v>0.1646</v>
       </c>
       <c r="AG13">
-        <v>1.3457</v>
+        <v>1.2379</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1970,10 +1970,10 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" t="s">
         <v>67</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
       </c>
       <c r="G14">
         <v>824882</v>
@@ -2027,7 +2027,7 @@
         <v>0.2174</v>
       </c>
       <c r="X14">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y14">
         <v>0.9698</v>
@@ -2039,7 +2039,7 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="AE14" t="s">
         <v>45</v>
@@ -2048,13 +2048,13 @@
         <v>0.1333</v>
       </c>
       <c r="AG14">
-        <v>0.9518</v>
+        <v>0.9705</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2062,10 +2062,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>824882</v>
@@ -2119,7 +2119,7 @@
         <v>0.1705</v>
       </c>
       <c r="X15">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y15">
         <v>0.88</v>
@@ -2131,7 +2131,7 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.41</v>
+        <v>5.51</v>
       </c>
       <c r="AE15" t="s">
         <v>45</v>
@@ -2140,13 +2140,13 @@
         <v>0.3316</v>
       </c>
       <c r="AG15">
-        <v>0.7876</v>
+        <v>0.803</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.41</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2154,10 +2154,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
         <v>70</v>
-      </c>
-      <c r="F16" t="s">
-        <v>71</v>
       </c>
       <c r="G16">
         <v>822777</v>
@@ -2196,13 +2196,13 @@
         <v>0.379</v>
       </c>
       <c r="S16" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T16">
-        <v>0.1919</v>
+        <v>0.1745</v>
       </c>
       <c r="U16">
-        <v>0.1802</v>
+        <v>0.1706</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -2211,10 +2211,10 @@
         <v>0.1887</v>
       </c>
       <c r="X16">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y16">
-        <v>0.9732</v>
+        <v>0.9663</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2223,7 +2223,7 @@
         <v>44</v>
       </c>
       <c r="AD16">
-        <v>5.72</v>
+        <v>5.26</v>
       </c>
       <c r="AE16" t="s">
         <v>45</v>
@@ -2232,13 +2232,13 @@
         <v>0.2885</v>
       </c>
       <c r="AG16">
-        <v>0.8663</v>
+        <v>0.8032</v>
       </c>
       <c r="AH16">
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>5.72</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2246,10 +2246,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17">
         <v>822777</v>
@@ -2288,13 +2288,13 @@
         <v>0.353</v>
       </c>
       <c r="S17" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2757</v>
+        <v>0.2581</v>
       </c>
       <c r="U17">
-        <v>0.2725</v>
+        <v>0.2626</v>
       </c>
       <c r="V17">
         <v>9</v>
@@ -2303,10 +2303,10 @@
         <v>0.2442</v>
       </c>
       <c r="X17">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y17">
-        <v>1.0039</v>
+        <v>1.0349</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2315,7 +2315,7 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
       <c r="AE17" t="s">
         <v>45</v>
@@ -2324,13 +2324,13 @@
         <v>0.1677</v>
       </c>
       <c r="AG17">
-        <v>1.2441</v>
+        <v>1.1876</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>4.54</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2338,10 +2338,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" t="s">
         <v>73</v>
-      </c>
-      <c r="F18" t="s">
-        <v>74</v>
       </c>
       <c r="G18">
         <v>824159</v>
@@ -2380,25 +2380,25 @@
         <v>0.357</v>
       </c>
       <c r="S18" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2132</v>
+        <v>0.2135</v>
       </c>
       <c r="U18">
-        <v>0.2026</v>
+        <v>0.2037</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>0.2162</v>
       </c>
       <c r="X18">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y18">
-        <v>1.0104</v>
+        <v>1.0117</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2407,7 +2407,7 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="AE18" t="s">
         <v>45</v>
@@ -2416,13 +2416,13 @@
         <v>0.2002</v>
       </c>
       <c r="AG18">
-        <v>0.9623</v>
+        <v>0.9823</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2430,10 +2430,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G19">
         <v>824159</v>
@@ -2472,25 +2472,25 @@
         <v>0.371</v>
       </c>
       <c r="S19" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T19">
-        <v>0.1987</v>
+        <v>0.1778</v>
       </c>
       <c r="U19">
-        <v>0.1883</v>
+        <v>0.182</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W19">
         <v>0.2256</v>
       </c>
       <c r="X19">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y19">
-        <v>0.9876</v>
+        <v>0.9748</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2499,7 +2499,7 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.06</v>
+        <v>4.56</v>
       </c>
       <c r="AE19" t="s">
         <v>45</v>
@@ -2508,13 +2508,13 @@
         <v>0.2422</v>
       </c>
       <c r="AG19">
-        <v>0.8966</v>
+        <v>0.8181</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.06</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2522,10 +2522,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
-      </c>
-      <c r="F20" t="s">
-        <v>77</v>
       </c>
       <c r="G20">
         <v>823993</v>
@@ -2564,13 +2564,13 @@
         <v>0.379</v>
       </c>
       <c r="S20" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2703</v>
+        <v>0.2187</v>
       </c>
       <c r="U20">
-        <v>0.2606</v>
+        <v>0.2278</v>
       </c>
       <c r="V20">
         <v>9</v>
@@ -2579,10 +2579,10 @@
         <v>0.2508</v>
       </c>
       <c r="X20">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y20">
-        <v>1.0327</v>
+        <v>0.9971</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2591,7 +2591,7 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.07</v>
+        <v>4.04</v>
       </c>
       <c r="AE20" t="s">
         <v>45</v>
@@ -2600,13 +2600,13 @@
         <v>0.1688</v>
       </c>
       <c r="AG20">
-        <v>1.2197</v>
+        <v>1.0065</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.07</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2614,10 +2614,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>823993</v>
@@ -2656,25 +2656,25 @@
         <v>0.351</v>
       </c>
       <c r="S21" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2016</v>
+        <v>0.1849</v>
       </c>
       <c r="U21">
-        <v>0.2044</v>
+        <v>0.197</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>0.2092</v>
       </c>
       <c r="X21">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y21">
-        <v>0.9531</v>
+        <v>0.9424</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2683,7 +2683,7 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AE21" t="s">
         <v>45</v>
@@ -2692,13 +2692,13 @@
         <v>0.2122</v>
       </c>
       <c r="AG21">
-        <v>0.91</v>
+        <v>0.8507</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2706,10 +2706,10 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
-      </c>
-      <c r="F22" t="s">
-        <v>80</v>
       </c>
       <c r="G22">
         <v>824968</v>
@@ -2748,7 +2748,7 @@
         <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="T22">
         <v>0.2603</v>
@@ -2763,7 +2763,7 @@
         <v>0.2168</v>
       </c>
       <c r="X22">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y22">
         <v>1.013</v>
@@ -2775,7 +2775,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.71</v>
+        <v>5.82</v>
       </c>
       <c r="AE22" t="s">
         <v>45</v>
@@ -2784,13 +2784,13 @@
         <v>0.2252</v>
       </c>
       <c r="AG22">
-        <v>1.1747</v>
+        <v>1.1977</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.71</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2840,7 +2840,7 @@
         <v>0.34</v>
       </c>
       <c r="S23" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="T23">
         <v>0.2813</v>
@@ -2855,7 +2855,7 @@
         <v>0.2008</v>
       </c>
       <c r="X23">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y23">
         <v>1.0004</v>
@@ -2867,7 +2867,7 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.87</v>
+        <v>5.99</v>
       </c>
       <c r="AE23" t="s">
         <v>45</v>
@@ -2876,13 +2876,13 @@
         <v>0.2101</v>
       </c>
       <c r="AG23">
-        <v>1.2697</v>
+        <v>1.2946</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.87</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2932,7 +2932,7 @@
         <v>0.403</v>
       </c>
       <c r="S24" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="T24">
         <v>0.2018</v>
@@ -2947,7 +2947,7 @@
         <v>0.2138</v>
       </c>
       <c r="X24">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y24">
         <v>1.0084</v>
@@ -2959,7 +2959,7 @@
         <v>44</v>
       </c>
       <c r="AD24">
-        <v>5.19</v>
+        <v>5.3</v>
       </c>
       <c r="AE24" t="s">
         <v>45</v>
@@ -2968,13 +2968,13 @@
         <v>0.2229</v>
       </c>
       <c r="AG24">
-        <v>0.9108</v>
+        <v>0.9286</v>
       </c>
       <c r="AH24">
         <v>0</v>
       </c>
       <c r="AM24">
-        <v>5.19</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3024,7 +3024,7 @@
         <v>0.396</v>
       </c>
       <c r="S25" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="T25">
         <v>0.2179</v>
@@ -3039,7 +3039,7 @@
         <v>0.2328</v>
       </c>
       <c r="X25">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y25">
         <v>0.9642</v>
@@ -3051,7 +3051,7 @@
         <v>44</v>
       </c>
       <c r="AD25">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
       <c r="AE25" t="s">
         <v>45</v>
@@ -3060,13 +3060,13 @@
         <v>0.1925</v>
       </c>
       <c r="AG25">
-        <v>0.9836</v>
+        <v>1.0029</v>
       </c>
       <c r="AH25">
         <v>0</v>
       </c>
       <c r="AM25">
-        <v>4.43</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3116,13 +3116,13 @@
         <v>0.357</v>
       </c>
       <c r="S26" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2267</v>
+        <v>0.2301</v>
       </c>
       <c r="U26">
-        <v>0.2247</v>
+        <v>0.207</v>
       </c>
       <c r="V26">
         <v>9</v>
@@ -3131,10 +3131,10 @@
         <v>0.2163</v>
       </c>
       <c r="X26">
-        <v>0.2216</v>
+        <v>0.2173</v>
       </c>
       <c r="Y26">
-        <v>1.0197</v>
+        <v>1.0107</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3143,7 +3143,7 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>5.04</v>
+        <v>5.16</v>
       </c>
       <c r="AE26" t="s">
         <v>45</v>
@@ -3152,13 +3152,13 @@
         <v>0.2126</v>
       </c>
       <c r="AG26">
-        <v>1.0233</v>
+        <v>1.059</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>5.04</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3178,7 +3178,7 @@
         <v>-101</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G27" t="s">
         <v>44</v>

--- a/data/k-props/2026-08-14.xlsx
+++ b/data/k-props/2026-08-14.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="92">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -154,12 +157,18 @@
     <t>Clay Holmes</t>
   </si>
   <si>
+    <t>U</t>
+  </si>
+  <si>
     <t>Sandy Alcantara</t>
   </si>
   <si>
     <t>Miami Marlins @ Cincinnati Reds</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>&gt;=7</t>
   </si>
   <si>
@@ -200,6 +209,9 @@
   </si>
   <si>
     <t>Gavin Williams</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>Chris Bassitt</t>
@@ -856,17 +868,23 @@
       <c r="Y2">
         <v>0.975</v>
       </c>
+      <c r="Z2">
+        <v>6</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>0.63</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>5.13</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2368</v>
@@ -876,6 +894,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.87</v>
+      </c>
+      <c r="AJ2">
+        <v>0.87</v>
+      </c>
+      <c r="AK2">
+        <v>0.87</v>
+      </c>
+      <c r="AL2">
+        <v>0.87</v>
       </c>
       <c r="AM2">
         <v>5.13</v>
@@ -886,7 +916,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>3.5</v>
@@ -957,17 +987,23 @@
       <c r="Y3">
         <v>0.9708</v>
       </c>
+      <c r="Z3">
+        <v>3</v>
+      </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB3">
+        <v>0.34</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD3">
         <v>3.84</v>
       </c>
       <c r="AE3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF3">
         <v>0.1995</v>
@@ -977,6 +1013,18 @@
       </c>
       <c r="AH3">
         <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>-0.84</v>
+      </c>
+      <c r="AJ3">
+        <v>0.84</v>
+      </c>
+      <c r="AK3">
+        <v>-0.84</v>
+      </c>
+      <c r="AL3">
+        <v>0.84</v>
       </c>
       <c r="AM3">
         <v>3.84</v>
@@ -987,7 +1035,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>5.5</v>
@@ -999,7 +1047,7 @@
         <v>102</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4">
         <v>824479</v>
@@ -1058,17 +1106,23 @@
       <c r="Y4">
         <v>1.062</v>
       </c>
+      <c r="Z4">
+        <v>2</v>
+      </c>
       <c r="AA4" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB4">
+        <v>1.92</v>
       </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="AD4">
         <v>8.22</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AF4">
         <v>0.1993</v>
@@ -1078,6 +1132,18 @@
       </c>
       <c r="AH4">
         <v>-0.8</v>
+      </c>
+      <c r="AI4">
+        <v>-6.22</v>
+      </c>
+      <c r="AJ4">
+        <v>6.22</v>
+      </c>
+      <c r="AK4">
+        <v>-5.42</v>
+      </c>
+      <c r="AL4">
+        <v>5.42</v>
       </c>
       <c r="AM4">
         <v>7.42</v>
@@ -1088,7 +1154,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>6.5</v>
@@ -1100,7 +1166,7 @@
         <v>-115</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G5">
         <v>824479</v>
@@ -1159,17 +1225,23 @@
       <c r="Y5">
         <v>0.8833</v>
       </c>
+      <c r="Z5">
+        <v>8</v>
+      </c>
       <c r="AA5" t="s">
         <v>44</v>
       </c>
+      <c r="AB5">
+        <v>-0.49</v>
+      </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD5">
         <v>6.01</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AF5">
         <v>0.2691</v>
@@ -1179,6 +1251,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>1.99</v>
+      </c>
+      <c r="AJ5">
+        <v>1.99</v>
+      </c>
+      <c r="AK5">
+        <v>1.99</v>
+      </c>
+      <c r="AL5">
+        <v>1.99</v>
       </c>
       <c r="AM5">
         <v>6.01</v>
@@ -1189,7 +1273,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>4.5</v>
@@ -1201,7 +1285,7 @@
         <v>-146</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>823346</v>
@@ -1260,17 +1344,23 @@
       <c r="Y6">
         <v>1.0839</v>
       </c>
+      <c r="Z6">
+        <v>6</v>
+      </c>
       <c r="AA6" t="s">
         <v>44</v>
       </c>
+      <c r="AB6">
+        <v>0.54</v>
+      </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>5.04</v>
       </c>
       <c r="AE6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF6">
         <v>0.1736</v>
@@ -1280,6 +1370,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0.96</v>
+      </c>
+      <c r="AJ6">
+        <v>0.96</v>
+      </c>
+      <c r="AK6">
+        <v>0.96</v>
+      </c>
+      <c r="AL6">
+        <v>0.96</v>
       </c>
       <c r="AM6">
         <v>5.04</v>
@@ -1290,7 +1392,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>4.5</v>
@@ -1302,7 +1404,7 @@
         <v>-146</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>823346</v>
@@ -1361,17 +1463,23 @@
       <c r="Y7">
         <v>0.9909</v>
       </c>
+      <c r="Z7">
+        <v>5</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>-0.66</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD7">
         <v>3.84</v>
       </c>
       <c r="AE7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF7">
         <v>0.2096</v>
@@ -1381,6 +1489,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>1.16</v>
+      </c>
+      <c r="AJ7">
+        <v>1.16</v>
+      </c>
+      <c r="AK7">
+        <v>1.16</v>
+      </c>
+      <c r="AL7">
+        <v>1.16</v>
       </c>
       <c r="AM7">
         <v>3.84</v>
@@ -1391,16 +1511,16 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>824237</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I8">
         <v>3</v>
@@ -1454,16 +1574,16 @@
         <v>0.88</v>
       </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD8">
         <v>2.36</v>
       </c>
       <c r="AE8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF8">
         <v>0.2375</v>
@@ -1483,10 +1603,10 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G9">
         <v>823591</v>
@@ -1546,16 +1666,16 @@
         <v>0.9762</v>
       </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD9">
         <v>4.12</v>
       </c>
       <c r="AE9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF9">
         <v>0.1953</v>
@@ -1575,7 +1695,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>3.5</v>
@@ -1587,7 +1707,7 @@
         <v>132</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G10">
         <v>824399</v>
@@ -1646,17 +1766,23 @@
       <c r="Y10">
         <v>0.88</v>
       </c>
+      <c r="Z10">
+        <v>4</v>
+      </c>
       <c r="AA10" t="s">
         <v>44</v>
       </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD10">
         <v>3.5</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2245</v>
@@ -1666,6 +1792,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0.5</v>
+      </c>
+      <c r="AJ10">
+        <v>0.5</v>
+      </c>
+      <c r="AK10">
+        <v>0.5</v>
+      </c>
+      <c r="AL10">
+        <v>0.5</v>
       </c>
       <c r="AM10">
         <v>3.5</v>
@@ -1676,7 +1814,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>7.5</v>
@@ -1688,7 +1826,7 @@
         <v>-155</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G11">
         <v>824399</v>
@@ -1747,17 +1885,23 @@
       <c r="Y11">
         <v>0.9878</v>
       </c>
+      <c r="Z11">
+        <v>5</v>
+      </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>48</v>
+      </c>
+      <c r="AB11">
+        <v>-0.73</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="AD11">
         <v>6.77</v>
       </c>
       <c r="AE11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AF11">
         <v>0.3692</v>
@@ -1767,6 +1911,18 @@
       </c>
       <c r="AH11">
         <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-1.77</v>
+      </c>
+      <c r="AJ11">
+        <v>1.77</v>
+      </c>
+      <c r="AK11">
+        <v>-1.77</v>
+      </c>
+      <c r="AL11">
+        <v>1.77</v>
       </c>
       <c r="AM11">
         <v>6.77</v>
@@ -1777,7 +1933,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1789,7 +1945,7 @@
         <v>145</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G12">
         <v>822942</v>
@@ -1848,17 +2004,23 @@
       <c r="Y12">
         <v>0.88</v>
       </c>
+      <c r="Z12">
+        <v>3</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>-0.14</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>2.36</v>
       </c>
       <c r="AE12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF12">
         <v>0.1463</v>
@@ -1868,6 +2030,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0.64</v>
+      </c>
+      <c r="AJ12">
+        <v>0.64</v>
+      </c>
+      <c r="AK12">
+        <v>0.64</v>
+      </c>
+      <c r="AL12">
+        <v>0.64</v>
       </c>
       <c r="AM12">
         <v>2.36</v>
@@ -1878,10 +2052,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>822942</v>
@@ -1941,16 +2115,16 @@
         <v>1.0594</v>
       </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD13">
         <v>4.2</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF13">
         <v>0.1646</v>
@@ -1970,10 +2144,10 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G14">
         <v>824882</v>
@@ -2033,16 +2207,16 @@
         <v>0.9698</v>
       </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD14">
         <v>3.05</v>
       </c>
       <c r="AE14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF14">
         <v>0.1333</v>
@@ -2062,10 +2236,10 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G15">
         <v>824882</v>
@@ -2125,16 +2299,16 @@
         <v>0.88</v>
       </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD15">
         <v>5.51</v>
       </c>
       <c r="AE15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF15">
         <v>0.3316</v>
@@ -2154,10 +2328,10 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G16">
         <v>822777</v>
@@ -2217,16 +2391,16 @@
         <v>0.9663</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD16">
         <v>5.26</v>
       </c>
       <c r="AE16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF16">
         <v>0.2885</v>
@@ -2246,10 +2420,10 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>822777</v>
@@ -2309,16 +2483,16 @@
         <v>1.0349</v>
       </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>4.47</v>
       </c>
       <c r="AE17" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF17">
         <v>0.1677</v>
@@ -2338,10 +2512,10 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18">
         <v>824159</v>
@@ -2401,16 +2575,16 @@
         <v>1.0117</v>
       </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD18">
         <v>4.91</v>
       </c>
       <c r="AE18" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF18">
         <v>0.2002</v>
@@ -2430,10 +2604,10 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G19">
         <v>824159</v>
@@ -2493,16 +2667,16 @@
         <v>0.9748</v>
       </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD19">
         <v>4.56</v>
       </c>
       <c r="AE19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF19">
         <v>0.2422</v>
@@ -2522,10 +2696,10 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>823993</v>
@@ -2585,16 +2759,16 @@
         <v>0.9971</v>
       </c>
       <c r="AA20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD20">
         <v>4.04</v>
       </c>
       <c r="AE20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF20">
         <v>0.1688</v>
@@ -2614,10 +2788,10 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G21">
         <v>823993</v>
@@ -2677,16 +2851,16 @@
         <v>0.9424</v>
       </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD21">
         <v>3.6</v>
       </c>
       <c r="AE21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF21">
         <v>0.2122</v>
@@ -2706,10 +2880,10 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G22">
         <v>824968</v>
@@ -2748,7 +2922,7 @@
         <v>0.373</v>
       </c>
       <c r="S22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T22">
         <v>0.2603</v>
@@ -2769,16 +2943,16 @@
         <v>1.013</v>
       </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD22">
         <v>5.82</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2252</v>
@@ -2798,10 +2972,10 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F23" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23">
         <v>823913</v>
@@ -2840,7 +3014,7 @@
         <v>0.34</v>
       </c>
       <c r="S23" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T23">
         <v>0.2813</v>
@@ -2861,16 +3035,16 @@
         <v>1.0004</v>
       </c>
       <c r="AA23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>5.99</v>
       </c>
       <c r="AE23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF23">
         <v>0.2101</v>
@@ -2890,10 +3064,10 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G24">
         <v>823913</v>
@@ -2932,7 +3106,7 @@
         <v>0.403</v>
       </c>
       <c r="S24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T24">
         <v>0.2018</v>
@@ -2953,16 +3127,16 @@
         <v>1.0084</v>
       </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD24">
         <v>5.3</v>
       </c>
       <c r="AE24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF24">
         <v>0.2229</v>
@@ -2982,10 +3156,10 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G25">
         <v>823185</v>
@@ -3024,7 +3198,7 @@
         <v>0.396</v>
       </c>
       <c r="S25" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="T25">
         <v>0.2179</v>
@@ -3045,16 +3219,16 @@
         <v>0.9642</v>
       </c>
       <c r="AA25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD25">
         <v>4.51</v>
       </c>
       <c r="AE25" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF25">
         <v>0.1925</v>
@@ -3074,10 +3248,10 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G26">
         <v>823185</v>
@@ -3137,16 +3311,16 @@
         <v>1.0107</v>
       </c>
       <c r="AA26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD26">
         <v>5.16</v>
       </c>
       <c r="AE26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF26">
         <v>0.2126</v>
@@ -3166,7 +3340,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C27">
         <v>4.5</v>
@@ -3178,31 +3352,34 @@
         <v>-101</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="S27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V27" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="Z27">
+        <v>4</v>
       </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
